--- a/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>VMAR</t>
   </si>
@@ -656,151 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45169</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45077</v>
+      </c>
+      <c r="G7" s="2">
         <v>44985</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>44895</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>44804</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44712</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44620</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44530</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44439</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44347</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44255</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44165</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>43524</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>43434</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="3">
         <v>600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="H8" s="3">
         <v>1000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="I8" s="3">
         <v>2500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
         <v>1500</v>
-      </c>
-      <c r="H8" s="3">
-        <v>600</v>
-      </c>
-      <c r="I8" s="3">
-        <v>900</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1700</v>
       </c>
       <c r="K8" s="3">
         <v>600</v>
       </c>
       <c r="L8" s="3">
+        <v>900</v>
+      </c>
+      <c r="M8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N8" s="3">
+        <v>600</v>
+      </c>
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="R8" s="3">
         <v>700</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="E9" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F9" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="G9" s="3">
         <v>600</v>
       </c>
       <c r="H9" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="I9" s="3">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J9" s="3">
         <v>700</v>
@@ -809,72 +829,90 @@
         <v>400</v>
       </c>
       <c r="L9" s="3">
+        <v>500</v>
+      </c>
+      <c r="M9" s="3">
+        <v>700</v>
+      </c>
+      <c r="N9" s="3">
+        <v>400</v>
+      </c>
+      <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="Q9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="R9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
+        <v>700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="I10" s="3">
         <v>1000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="J10" s="3">
         <v>800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="L10" s="3">
         <v>400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
         <v>1000</v>
-      </c>
-      <c r="K10" s="3">
-        <v>100</v>
-      </c>
-      <c r="L10" s="3">
-        <v>100</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0</v>
       </c>
       <c r="N10" s="3">
         <v>100</v>
       </c>
       <c r="O10" s="3">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>100</v>
+      </c>
+      <c r="R10" s="3">
         <v>300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,55 +930,67 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>700</v>
+      </c>
+      <c r="E12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
+        <v>600</v>
+      </c>
+      <c r="G12" s="3">
+        <v>500</v>
+      </c>
+      <c r="H12" s="3">
         <v>2700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="I12" s="3">
         <v>1600</v>
       </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="L12" s="3">
         <v>-100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="M12" s="3">
         <v>800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
+      <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,25 +1036,34 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>1900</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1015,11 +1074,11 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1033,55 +1092,73 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
       </c>
       <c r="F15" s="3">
+        <v>200</v>
+      </c>
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1173,123 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5500</v>
+        <v>-100</v>
       </c>
       <c r="E17" s="3">
-        <v>5900</v>
+        <v>4800</v>
       </c>
       <c r="F17" s="3">
-        <v>5200</v>
+        <v>3400</v>
       </c>
       <c r="G17" s="3">
-        <v>2800</v>
+        <v>5600</v>
       </c>
       <c r="H17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K17" s="3">
         <v>3300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>3300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>4400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>4100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>3500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="R17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-4900</v>
+        <v>800</v>
       </c>
       <c r="E18" s="3">
-        <v>-4900</v>
+        <v>-3200</v>
       </c>
       <c r="F18" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-2800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3">
         <v>-2700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-2500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>-2800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>-3500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>-3300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="R18" s="3">
         <v>100</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,13 +1307,16 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1250,61 +1351,79 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-4700</v>
+        <v>900</v>
       </c>
       <c r="E21" s="3">
-        <v>-4700</v>
+        <v>-3000</v>
       </c>
       <c r="F21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K21" s="3">
         <v>-2600</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="L21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="M21" s="3">
         <v>-2600</v>
       </c>
-      <c r="I21" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="N21" s="3">
         <v>-3400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="O21" s="3">
         <v>-3300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="P21" s="3">
         <v>-1400</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1350,55 +1469,73 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-4900</v>
+        <v>700</v>
       </c>
       <c r="E23" s="3">
-        <v>-4900</v>
+        <v>-3200</v>
       </c>
       <c r="F23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2800</v>
       </c>
-      <c r="G23" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>-2500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>-2800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>-3400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="R23" s="3">
         <v>100</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1406,19 +1543,19 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="G24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
@@ -1430,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1438,14 +1575,23 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1637,129 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-4900</v>
+        <v>800</v>
       </c>
       <c r="E26" s="3">
-        <v>-4900</v>
+        <v>-3200</v>
       </c>
       <c r="F26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M26" s="3">
         <v>-2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="N26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="H26" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="R26" s="3">
         <v>100</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-4900</v>
+        <v>800</v>
       </c>
       <c r="E27" s="3">
-        <v>-4900</v>
+        <v>-3200</v>
       </c>
       <c r="F27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M27" s="3">
         <v>-2900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="N27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="H27" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="R27" s="3">
         <v>100</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,8 +1805,17 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1679,8 +1861,17 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1917,17 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,13 +1973,22 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1814,61 +2023,79 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-4900</v>
+        <v>800</v>
       </c>
       <c r="E33" s="3">
-        <v>-4900</v>
+        <v>-3200</v>
       </c>
       <c r="F33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M33" s="3">
         <v>-2900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="N33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="H33" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="R33" s="3">
         <v>100</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +2141,134 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-4900</v>
+        <v>800</v>
       </c>
       <c r="E35" s="3">
-        <v>-4900</v>
+        <v>-3200</v>
       </c>
       <c r="F35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M35" s="3">
         <v>-2900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="N35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="H35" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="R35" s="3">
         <v>100</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45169</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45077</v>
+      </c>
+      <c r="G38" s="2">
         <v>44985</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>44895</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>44804</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44712</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44620</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44530</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44439</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44347</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44255</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44165</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>43524</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>43434</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2286,11 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,41 +2308,44 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G41" s="3">
         <v>3000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>5700</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="J41" s="3">
+        <v>5800</v>
+      </c>
+      <c r="K41" s="3">
         <v>7100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>10600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>13200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2098,8 +2358,17 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2133,53 +2402,62 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>500</v>
+      </c>
+      <c r="F43" s="3">
+        <v>600</v>
+      </c>
+      <c r="G43" s="3">
         <v>700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
+        <v>900</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K43" s="3">
         <v>800</v>
       </c>
-      <c r="G43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H43" s="3">
-        <v>800</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,41 +2470,50 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G44" s="3">
         <v>1900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I44" s="3">
         <v>1500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="J44" s="3">
         <v>2400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>2200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>2000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>1400</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2239,41 +2526,50 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F45" s="3">
+        <v>800</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J45" s="3">
         <v>2500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,41 +2582,50 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>6100</v>
+        <v>5500</v>
       </c>
       <c r="E46" s="3">
-        <v>4700</v>
+        <v>6300</v>
       </c>
       <c r="F46" s="3">
-        <v>8400</v>
+        <v>4500</v>
       </c>
       <c r="G46" s="3">
-        <v>11600</v>
+        <v>6200</v>
       </c>
       <c r="H46" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I46" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J46" s="3">
+        <v>11800</v>
+      </c>
+      <c r="K46" s="3">
         <v>12200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>14100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>15500</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,8 +2638,17 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2342,46 +2656,55 @@
         <v>100</v>
       </c>
       <c r="E47" s="3">
+        <v>100</v>
+      </c>
+      <c r="F47" s="3">
+        <v>100</v>
+      </c>
+      <c r="G47" s="3">
+        <v>100</v>
+      </c>
+      <c r="H47" s="3">
         <v>2000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="I47" s="3">
         <v>1900</v>
       </c>
-      <c r="G47" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K47" s="3">
         <v>1500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>2100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>2100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2389,32 +2712,32 @@
         <v>3300</v>
       </c>
       <c r="E48" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="F48" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G48" s="3">
         <v>3300</v>
       </c>
-      <c r="G48" s="3">
-        <v>3200</v>
-      </c>
       <c r="H48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="I48" s="3">
         <v>3300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L48" s="3">
         <v>3100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>3100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2427,40 +2750,49 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="E49" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="F49" s="3">
-        <v>7600</v>
+        <v>7900</v>
       </c>
       <c r="G49" s="3">
-        <v>7400</v>
+        <v>7900</v>
       </c>
       <c r="H49" s="3">
-        <v>7400</v>
+        <v>8000</v>
       </c>
       <c r="I49" s="3">
-        <v>7500</v>
+        <v>7700</v>
       </c>
       <c r="J49" s="3">
         <v>7500</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>7400</v>
+      </c>
+      <c r="L49" s="3">
+        <v>7500</v>
+      </c>
+      <c r="M49" s="3">
+        <v>7500</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2468,14 +2800,23 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2862,17 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,25 +2918,34 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="D52" s="3">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>100</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -2594,14 +2953,14 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2609,14 +2968,23 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,41 +3030,50 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>17200</v>
+        <v>16900</v>
       </c>
       <c r="E54" s="3">
-        <v>18000</v>
+        <v>17800</v>
       </c>
       <c r="F54" s="3">
-        <v>21200</v>
+        <v>16200</v>
       </c>
       <c r="G54" s="3">
-        <v>24100</v>
+        <v>17500</v>
       </c>
       <c r="H54" s="3">
+        <v>18300</v>
+      </c>
+      <c r="I54" s="3">
+        <v>21500</v>
+      </c>
+      <c r="J54" s="3">
+        <v>24500</v>
+      </c>
+      <c r="K54" s="3">
         <v>24400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>26900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>28200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2709,8 +3086,17 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +3114,11 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,41 +3136,44 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>800</v>
+      </c>
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H57" s="3">
         <v>1600</v>
-      </c>
-      <c r="F57" s="3">
-        <v>500</v>
-      </c>
-      <c r="G57" s="3">
-        <v>500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>400</v>
       </c>
       <c r="I57" s="3">
         <v>500</v>
       </c>
       <c r="J57" s="3">
+        <v>500</v>
+      </c>
+      <c r="K57" s="3">
+        <v>400</v>
+      </c>
+      <c r="L57" s="3">
+        <v>500</v>
+      </c>
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,41 +3186,50 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>900</v>
+      </c>
+      <c r="G58" s="3">
         <v>1400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2841,41 +3242,50 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1100</v>
-      </c>
       <c r="G59" s="3">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="H59" s="3">
         <v>1100</v>
       </c>
       <c r="I59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2888,41 +3298,50 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F60" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G60" s="3">
         <v>3400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>3200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>2100</v>
       </c>
-      <c r="G60" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K60" s="3">
         <v>2000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>1900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>2000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2935,8 +3354,17 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2947,29 +3375,29 @@
         <v>1500</v>
       </c>
       <c r="F61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H61" s="3">
         <v>1500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J61" s="3">
         <v>1600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>1700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>1700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>1800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2982,22 +3410,31 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F62" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G62" s="3">
         <v>2900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>100</v>
       </c>
       <c r="H62" s="3">
         <v>100</v>
@@ -3008,14 +3445,14 @@
       <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>100</v>
+      </c>
+      <c r="L62" s="3">
+        <v>100</v>
+      </c>
+      <c r="M62" s="3">
+        <v>100</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
@@ -3029,8 +3466,17 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3522,17 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3578,17 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,41 +3634,50 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>7600</v>
+        <v>6500</v>
       </c>
       <c r="E66" s="3">
-        <v>4800</v>
+        <v>9200</v>
       </c>
       <c r="F66" s="3">
+        <v>7100</v>
+      </c>
+      <c r="G66" s="3">
+        <v>7700</v>
+      </c>
+      <c r="H66" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I66" s="3">
         <v>3700</v>
       </c>
-      <c r="G66" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K66" s="3">
         <v>3800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>3800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>3800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,8 +3690,17 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3718,11 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3768,17 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3824,17 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3880,17 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,41 +3936,50 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-24100</v>
+        <v>-28600</v>
       </c>
       <c r="E72" s="3">
-        <v>-19300</v>
+        <v>-29500</v>
       </c>
       <c r="F72" s="3">
-        <v>-14600</v>
+        <v>-26300</v>
       </c>
       <c r="G72" s="3">
-        <v>-11800</v>
+        <v>-24500</v>
       </c>
       <c r="H72" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="I72" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-11000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>-8400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>-7100</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3992,17 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +4048,17 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +4104,17 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,41 +4160,50 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9700</v>
+        <v>10400</v>
       </c>
       <c r="E76" s="3">
-        <v>13100</v>
+        <v>8500</v>
       </c>
       <c r="F76" s="3">
-        <v>17500</v>
+        <v>9100</v>
       </c>
       <c r="G76" s="3">
-        <v>20000</v>
+        <v>9800</v>
       </c>
       <c r="H76" s="3">
+        <v>13300</v>
+      </c>
+      <c r="I76" s="3">
+        <v>17800</v>
+      </c>
+      <c r="J76" s="3">
+        <v>20300</v>
+      </c>
+      <c r="K76" s="3">
         <v>20600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>23100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>24400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,8 +4216,17 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +4272,134 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45169</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45077</v>
+      </c>
+      <c r="G80" s="2">
         <v>44985</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>44895</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>44804</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44712</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44620</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44530</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44439</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44347</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44255</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44165</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>43524</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>43434</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-4900</v>
+        <v>800</v>
       </c>
       <c r="E81" s="3">
-        <v>-4900</v>
+        <v>-3200</v>
       </c>
       <c r="F81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="M81" s="3">
         <v>-2900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="N81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="O81" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="H81" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="R81" s="3">
         <v>100</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4417,11 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3848,31 +4444,40 @@
         <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
+        <v>100</v>
+      </c>
+      <c r="P83" s="3">
+        <v>100</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4523,17 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4579,17 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4635,17 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4691,17 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,55 +4747,73 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="G89" s="3">
         <v>-2400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>-2900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>-1100</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K89" s="3">
         <v>-3200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>-2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>-2400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>-1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>-1500</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,55 +4831,67 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4937,17 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,8 +4993,17 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4331,37 +5020,46 @@
         <v>-100</v>
       </c>
       <c r="H94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-3900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-2600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +5077,11 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4426,8 +5127,17 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +5183,17 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +5239,17 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,55 +5295,73 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>4200</v>
+        <v>1200</v>
       </c>
       <c r="E100" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G100" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="I100" s="3">
         <v>-200</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H100" s="3">
-        <v>100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
       </c>
       <c r="J100" s="3">
         <v>-100</v>
       </c>
       <c r="K100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>26600</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4661,51 +5407,69 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G102" s="3">
         <v>1800</v>
       </c>
-      <c r="E102" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>-1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>-3500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>-4300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>-5100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-2800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>25100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
@@ -656,133 +656,137 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E7" s="2">
         <v>45260</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45169</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45077</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44985</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44895</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44804</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44712</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44620</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44530</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44439</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44347</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44255</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44165</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43524</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43434</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3">
         <v>700</v>
       </c>
-      <c r="E8" s="3">
-        <v>1600</v>
-      </c>
       <c r="F8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G8" s="3">
+        <v>900</v>
+      </c>
+      <c r="H8" s="3">
+        <v>600</v>
+      </c>
+      <c r="I8" s="3">
         <v>1000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L8" s="3">
         <v>600</v>
       </c>
-      <c r="H8" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
+        <v>900</v>
+      </c>
+      <c r="N8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O8" s="3">
         <v>600</v>
-      </c>
-      <c r="L8" s="3">
-        <v>900</v>
-      </c>
-      <c r="M8" s="3">
-        <v>1700</v>
-      </c>
-      <c r="N8" s="3">
-        <v>600</v>
-      </c>
-      <c r="O8" s="3">
-        <v>200</v>
       </c>
       <c r="P8" s="3">
         <v>200</v>
@@ -791,16 +795,19 @@
         <v>200</v>
       </c>
       <c r="R8" s="3">
+        <v>200</v>
+      </c>
+      <c r="S8" s="3">
         <v>700</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -808,111 +815,117 @@
         <v>400</v>
       </c>
       <c r="E9" s="3">
+        <v>400</v>
+      </c>
+      <c r="F9" s="3">
         <v>800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>600</v>
       </c>
-      <c r="H9" s="3">
-        <v>1000</v>
-      </c>
       <c r="I9" s="3">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="J9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>400</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
       <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1000</v>
-      </c>
-      <c r="N10" s="3">
-        <v>100</v>
       </c>
       <c r="O10" s="3">
         <v>100</v>
       </c>
       <c r="P10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3">
         <v>100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,52 +946,53 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
         <v>700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>500</v>
-      </c>
-      <c r="F12" s="3">
-        <v>600</v>
       </c>
       <c r="G12" s="3">
         <v>500</v>
       </c>
       <c r="H12" s="3">
+        <v>500</v>
+      </c>
+      <c r="I12" s="3">
         <v>2700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1600</v>
       </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
       <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>-100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
       <c r="P12" s="3">
         <v>0</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
+      <c r="Q12" s="3">
+        <v>0</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,43 +1062,46 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1101,8 +1121,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1113,7 +1136,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
@@ -1125,7 +1148,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1134,11 +1157,11 @@
         <v>0</v>
       </c>
       <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1151,14 +1174,17 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E17" s="3">
         <v>-100</v>
       </c>
-      <c r="E17" s="3">
-        <v>4800</v>
-      </c>
       <c r="F17" s="3">
-        <v>3400</v>
+        <v>4700</v>
       </c>
       <c r="G17" s="3">
-        <v>5600</v>
+        <v>3300</v>
       </c>
       <c r="H17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I17" s="3">
         <v>6000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2900</v>
-      </c>
-      <c r="K17" s="3">
-        <v>3300</v>
       </c>
       <c r="L17" s="3">
         <v>3300</v>
       </c>
       <c r="M17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N17" s="3">
         <v>4400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E18" s="3">
         <v>800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2400</v>
       </c>
-      <c r="G18" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H18" s="3">
-        <v>-5000</v>
+        <v>-4900</v>
       </c>
       <c r="I18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-2800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,17 +1343,18 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
@@ -1360,61 +1394,64 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E21" s="3">
         <v>900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-4800</v>
-      </c>
       <c r="H21" s="3">
-        <v>-4800</v>
+        <v>-4700</v>
       </c>
       <c r="I21" s="3">
-        <v>-2700</v>
+        <v>-4700</v>
       </c>
       <c r="J21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
+      <c r="R21" s="3">
+        <v>0</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
@@ -1422,8 +1459,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1478,64 +1518,70 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E23" s="3">
         <v>700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2400</v>
       </c>
-      <c r="G23" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H23" s="3">
-        <v>-5000</v>
+        <v>-4900</v>
       </c>
       <c r="I23" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="J23" s="3">
         <v>-2800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>100</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1543,35 +1589,35 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F24" s="3">
         <v>-100</v>
       </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1584,14 +1630,17 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>800</v>
+        <v>-6100</v>
       </c>
       <c r="E26" s="3">
-        <v>-3200</v>
+        <v>700</v>
       </c>
       <c r="F26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="G26" s="3">
         <v>-2300</v>
       </c>
-      <c r="G26" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H26" s="3">
-        <v>-5000</v>
+        <v>-4900</v>
       </c>
       <c r="I26" s="3">
-        <v>-3000</v>
+        <v>-4900</v>
       </c>
       <c r="J26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>100</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>800</v>
+        <v>-6100</v>
       </c>
       <c r="E27" s="3">
-        <v>-3200</v>
+        <v>700</v>
       </c>
       <c r="F27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="G27" s="3">
         <v>-2300</v>
       </c>
-      <c r="G27" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H27" s="3">
-        <v>-5000</v>
+        <v>-4900</v>
       </c>
       <c r="I27" s="3">
-        <v>-3000</v>
+        <v>-4900</v>
       </c>
       <c r="J27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>100</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,17 +2049,20 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
@@ -2032,70 +2102,76 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>800</v>
+        <v>-6100</v>
       </c>
       <c r="E33" s="3">
-        <v>-3200</v>
+        <v>700</v>
       </c>
       <c r="F33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="G33" s="3">
         <v>-2300</v>
       </c>
-      <c r="G33" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H33" s="3">
-        <v>-5000</v>
+        <v>-4900</v>
       </c>
       <c r="I33" s="3">
-        <v>-3000</v>
+        <v>-4900</v>
       </c>
       <c r="J33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>100</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>800</v>
+        <v>-6100</v>
       </c>
       <c r="E35" s="3">
-        <v>-3200</v>
+        <v>700</v>
       </c>
       <c r="F35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="G35" s="3">
         <v>-2300</v>
       </c>
-      <c r="G35" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H35" s="3">
-        <v>-5000</v>
+        <v>-4900</v>
       </c>
       <c r="I35" s="3">
-        <v>-3000</v>
+        <v>-4900</v>
       </c>
       <c r="J35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>100</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E38" s="2">
         <v>45260</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45169</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45077</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44985</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44895</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44804</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44712</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44620</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44530</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44439</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44347</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44255</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44165</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43524</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43434</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,44 +2397,45 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>900</v>
+      </c>
+      <c r="E41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
-        <v>2500</v>
-      </c>
       <c r="F41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G41" s="3">
         <v>1100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1200</v>
       </c>
-      <c r="I41" s="3">
-        <v>4300</v>
-      </c>
       <c r="J41" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K41" s="3">
         <v>5800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,8 +2454,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2411,8 +2501,8 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
+      <c r="Q42" s="3">
+        <v>0</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
@@ -2423,44 +2513,47 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
         <v>400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>600</v>
-      </c>
-      <c r="G43" s="3">
-        <v>700</v>
       </c>
       <c r="H43" s="3">
         <v>700</v>
       </c>
       <c r="I43" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="J43" s="3">
+        <v>800</v>
+      </c>
+      <c r="K43" s="3">
         <v>1100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2479,44 +2572,47 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H44" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J44" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K44" s="3">
         <v>2400</v>
       </c>
-      <c r="E44" s="3">
-        <v>1800</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="L44" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M44" s="3">
         <v>2000</v>
       </c>
-      <c r="G44" s="3">
-        <v>1900</v>
-      </c>
-      <c r="H44" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I44" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J44" s="3">
-        <v>2400</v>
-      </c>
-      <c r="K44" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L44" s="3">
-        <v>2000</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1400</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2535,44 +2631,47 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E45" s="3">
         <v>2100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
-        <v>1900</v>
-      </c>
       <c r="J45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K45" s="3">
         <v>2500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2591,44 +2690,47 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E46" s="3">
         <v>5500</v>
       </c>
-      <c r="E46" s="3">
-        <v>6300</v>
-      </c>
       <c r="F46" s="3">
-        <v>4500</v>
+        <v>6200</v>
       </c>
       <c r="G46" s="3">
-        <v>6200</v>
+        <v>4400</v>
       </c>
       <c r="H46" s="3">
-        <v>4800</v>
+        <v>6100</v>
       </c>
       <c r="I46" s="3">
-        <v>8600</v>
+        <v>4700</v>
       </c>
       <c r="J46" s="3">
+        <v>8500</v>
+      </c>
+      <c r="K46" s="3">
         <v>11800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15500</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,8 +2749,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2665,25 +2770,25 @@
         <v>100</v>
       </c>
       <c r="H47" s="3">
+        <v>100</v>
+      </c>
+      <c r="I47" s="3">
         <v>2000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>1900</v>
       </c>
       <c r="J47" s="3">
         <v>1900</v>
       </c>
       <c r="K47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L47" s="3">
         <v>1500</v>
-      </c>
-      <c r="L47" s="3">
-        <v>2100</v>
       </c>
       <c r="M47" s="3">
         <v>2100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
+      <c r="N47" s="3">
+        <v>2100</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
@@ -2697,34 +2802,37 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
       </c>
-      <c r="E48" s="3">
-        <v>3500</v>
-      </c>
       <c r="F48" s="3">
-        <v>3700</v>
+        <v>3400</v>
       </c>
       <c r="G48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H48" s="3">
         <v>3300</v>
       </c>
-      <c r="H48" s="3">
-        <v>3500</v>
-      </c>
       <c r="I48" s="3">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="J48" s="3">
         <v>3300</v>
@@ -2733,13 +2841,13 @@
         <v>3300</v>
       </c>
       <c r="L48" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="M48" s="3">
         <v>3100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3">
+        <v>3100</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
@@ -2759,43 +2867,46 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F49" s="3">
+        <v>7800</v>
+      </c>
+      <c r="G49" s="3">
+        <v>7800</v>
+      </c>
+      <c r="H49" s="3">
+        <v>7800</v>
+      </c>
+      <c r="I49" s="3">
         <v>7900</v>
       </c>
-      <c r="E49" s="3">
-        <v>7900</v>
-      </c>
-      <c r="F49" s="3">
-        <v>7900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>7900</v>
-      </c>
-      <c r="H49" s="3">
-        <v>8000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>7700</v>
-      </c>
       <c r="J49" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K49" s="3">
         <v>7500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7400</v>
-      </c>
-      <c r="L49" s="3">
-        <v>7500</v>
       </c>
       <c r="M49" s="3">
         <v>7500</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="N49" s="3">
+        <v>7500</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
@@ -2809,14 +2920,17 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,8 +3044,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2938,8 +3058,8 @@
       <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="F52" s="3">
+        <v>0</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -2947,8 +3067,8 @@
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -2962,8 +3082,8 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2977,14 +3097,17 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,44 +3162,47 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16900</v>
+        <v>15500</v>
       </c>
       <c r="E54" s="3">
-        <v>17800</v>
+        <v>16700</v>
       </c>
       <c r="F54" s="3">
-        <v>16200</v>
+        <v>17500</v>
       </c>
       <c r="G54" s="3">
-        <v>17500</v>
+        <v>16000</v>
       </c>
       <c r="H54" s="3">
-        <v>18300</v>
+        <v>17300</v>
       </c>
       <c r="I54" s="3">
-        <v>21500</v>
+        <v>18000</v>
       </c>
       <c r="J54" s="3">
+        <v>21200</v>
+      </c>
+      <c r="K54" s="3">
         <v>24500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>28200</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3095,8 +3221,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,44 +3269,45 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1100</v>
       </c>
       <c r="G57" s="3">
         <v>1100</v>
       </c>
       <c r="H57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I57" s="3">
         <v>1600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>500</v>
       </c>
       <c r="J57" s="3">
         <v>500</v>
       </c>
       <c r="K57" s="3">
+        <v>500</v>
+      </c>
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3195,28 +3326,31 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="E58" s="3">
         <v>800</v>
       </c>
       <c r="F58" s="3">
+        <v>800</v>
+      </c>
+      <c r="G58" s="3">
         <v>900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>600</v>
-      </c>
-      <c r="I58" s="3">
-        <v>500</v>
       </c>
       <c r="J58" s="3">
         <v>500</v>
@@ -3225,13 +3359,13 @@
         <v>500</v>
       </c>
       <c r="L58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M58" s="3">
         <v>400</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3">
+        <v>400</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
@@ -3251,8 +3385,11 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3260,35 +3397,35 @@
         <v>1900</v>
       </c>
       <c r="E59" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="F59" s="3">
-        <v>900</v>
+        <v>1900</v>
       </c>
       <c r="G59" s="3">
         <v>900</v>
       </c>
       <c r="H59" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="I59" s="3">
         <v>1100</v>
       </c>
       <c r="J59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K59" s="3">
         <v>1500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3307,44 +3444,47 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E60" s="3">
         <v>4400</v>
       </c>
-      <c r="E60" s="3">
-        <v>3600</v>
-      </c>
       <c r="F60" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G60" s="3">
         <v>2900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3363,8 +3503,11 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3372,35 +3515,35 @@
         <v>1400</v>
       </c>
       <c r="E61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F61" s="3">
         <v>1500</v>
       </c>
-      <c r="F61" s="3">
-        <v>1700</v>
-      </c>
       <c r="G61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H61" s="3">
         <v>1400</v>
-      </c>
-      <c r="H61" s="3">
-        <v>1500</v>
       </c>
       <c r="I61" s="3">
         <v>1500</v>
       </c>
       <c r="J61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K61" s="3">
         <v>1600</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1700</v>
       </c>
       <c r="L61" s="3">
         <v>1700</v>
       </c>
       <c r="M61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N61" s="3">
         <v>1800</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3419,25 +3562,28 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E62" s="3">
         <v>700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2900</v>
-      </c>
-      <c r="H62" s="3">
-        <v>100</v>
       </c>
       <c r="I62" s="3">
         <v>100</v>
@@ -3454,8 +3600,8 @@
       <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="N62" s="3">
+        <v>100</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,34 +3798,37 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6500</v>
+        <v>10900</v>
       </c>
       <c r="E66" s="3">
-        <v>9200</v>
+        <v>6400</v>
       </c>
       <c r="F66" s="3">
-        <v>7100</v>
+        <v>9100</v>
       </c>
       <c r="G66" s="3">
-        <v>7700</v>
+        <v>7000</v>
       </c>
       <c r="H66" s="3">
-        <v>4900</v>
+        <v>7600</v>
       </c>
       <c r="I66" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J66" s="3">
         <v>3700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4200</v>
-      </c>
-      <c r="K66" s="3">
-        <v>3800</v>
       </c>
       <c r="L66" s="3">
         <v>3800</v>
@@ -3678,8 +3836,8 @@
       <c r="M66" s="3">
         <v>3800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
+      <c r="N66" s="3">
+        <v>3800</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
@@ -3699,8 +3857,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,44 +4116,47 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-28600</v>
+        <v>-34200</v>
       </c>
       <c r="E72" s="3">
-        <v>-29500</v>
+        <v>-28200</v>
       </c>
       <c r="F72" s="3">
-        <v>-26300</v>
+        <v>-29100</v>
       </c>
       <c r="G72" s="3">
-        <v>-24500</v>
+        <v>-26000</v>
       </c>
       <c r="H72" s="3">
-        <v>-19600</v>
+        <v>-24200</v>
       </c>
       <c r="I72" s="3">
-        <v>-14900</v>
+        <v>-19400</v>
       </c>
       <c r="J72" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="K72" s="3">
         <v>-12000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-11000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7100</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4001,8 +4175,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,44 +4352,47 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>10400</v>
+        <v>4700</v>
       </c>
       <c r="E76" s="3">
-        <v>8500</v>
+        <v>10300</v>
       </c>
       <c r="F76" s="3">
-        <v>9100</v>
+        <v>8400</v>
       </c>
       <c r="G76" s="3">
-        <v>9800</v>
+        <v>9000</v>
       </c>
       <c r="H76" s="3">
-        <v>13300</v>
+        <v>9700</v>
       </c>
       <c r="I76" s="3">
-        <v>17800</v>
+        <v>13200</v>
       </c>
       <c r="J76" s="3">
+        <v>17500</v>
+      </c>
+      <c r="K76" s="3">
         <v>20300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24400</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4225,8 +4411,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45351</v>
+      </c>
+      <c r="E80" s="2">
         <v>45260</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45169</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45077</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44985</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44895</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44804</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44712</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44620</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44530</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44439</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44347</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44255</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44165</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43524</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43434</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>800</v>
+        <v>-6100</v>
       </c>
       <c r="E81" s="3">
-        <v>-3200</v>
+        <v>700</v>
       </c>
       <c r="F81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="G81" s="3">
         <v>-2300</v>
       </c>
-      <c r="G81" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H81" s="3">
-        <v>-5000</v>
+        <v>-4900</v>
       </c>
       <c r="I81" s="3">
-        <v>-3000</v>
+        <v>-4900</v>
       </c>
       <c r="J81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>100</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4453,7 +4652,7 @@
         <v>200</v>
       </c>
       <c r="M83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -4464,8 +4663,8 @@
       <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>100</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4476,8 +4675,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,53 +4970,56 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
-        <v>-3100</v>
-      </c>
       <c r="G89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="H89" s="3">
         <v>-2400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4812,8 +5029,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,52 +5054,53 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-300</v>
       </c>
       <c r="H91" s="3">
         <v>-300</v>
       </c>
       <c r="I91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -4890,8 +5111,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,52 +5229,55 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-400</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5058,8 +5288,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,53 +5547,56 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1200</v>
+        <v>4700</v>
       </c>
       <c r="E100" s="3">
-        <v>3400</v>
+        <v>1100</v>
       </c>
       <c r="F100" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G100" s="3">
         <v>1300</v>
       </c>
-      <c r="G100" s="3">
-        <v>4300</v>
-      </c>
       <c r="H100" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>26600</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5360,8 +5606,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5416,53 +5665,56 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F102" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1900</v>
       </c>
-      <c r="E102" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1800</v>
       </c>
-      <c r="H102" s="3">
-        <v>-3100</v>
-      </c>
       <c r="I102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5470,6 +5722,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>VMAR</t>
   </si>
@@ -656,140 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E7" s="2">
         <v>45351</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45260</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45169</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45077</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44985</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44895</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44804</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44712</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44620</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44530</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44439</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44347</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44255</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44165</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43524</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43434</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>400</v>
+      </c>
+      <c r="E8" s="3">
         <v>500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>400</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M8" s="3">
+        <v>600</v>
+      </c>
+      <c r="N8" s="3">
         <v>900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="O8" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P8" s="3">
         <v>600</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J8" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1500</v>
-      </c>
-      <c r="L8" s="3">
-        <v>600</v>
-      </c>
-      <c r="M8" s="3">
-        <v>900</v>
-      </c>
-      <c r="N8" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O8" s="3">
-        <v>600</v>
-      </c>
-      <c r="P8" s="3">
-        <v>200</v>
       </c>
       <c r="Q8" s="3">
         <v>200</v>
@@ -798,16 +802,19 @@
         <v>200</v>
       </c>
       <c r="S8" s="3">
+        <v>200</v>
+      </c>
+      <c r="T8" s="3">
         <v>700</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -818,55 +825,58 @@
         <v>400</v>
       </c>
       <c r="F9" s="3">
+        <v>400</v>
+      </c>
+      <c r="G9" s="3">
         <v>800</v>
       </c>
-      <c r="G9" s="3">
-        <v>700</v>
-      </c>
       <c r="H9" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="I9" s="3">
         <v>900</v>
       </c>
       <c r="J9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K9" s="3">
         <v>1400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>400</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,58 +884,61 @@
         <v>100</v>
       </c>
       <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
         <v>300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>700</v>
       </c>
-      <c r="G10" s="3">
-        <v>300</v>
-      </c>
       <c r="H10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1000</v>
-      </c>
-      <c r="O10" s="3">
-        <v>100</v>
       </c>
       <c r="P10" s="3">
         <v>100</v>
       </c>
       <c r="Q10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10" s="3">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3">
         <v>100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,55 +960,56 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>700</v>
-      </c>
-      <c r="F12" s="3">
-        <v>500</v>
       </c>
       <c r="G12" s="3">
         <v>500</v>
       </c>
       <c r="H12" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J12" s="3">
         <v>2700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1600</v>
       </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
       <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>-100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
       <c r="Q12" s="3">
         <v>0</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
+      <c r="R12" s="3">
+        <v>0</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,46 +1082,49 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E14" s="3">
         <v>3100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>1900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1124,8 +1144,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1133,7 +1156,7 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1151,7 +1174,7 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1160,11 +1183,11 @@
         <v>0</v>
       </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>100</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1177,14 +1200,17 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
+      <c r="T15" s="3">
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5400</v>
+        <v>2900</v>
       </c>
       <c r="E17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F17" s="3">
         <v>-100</v>
       </c>
-      <c r="F17" s="3">
-        <v>4700</v>
-      </c>
       <c r="G17" s="3">
-        <v>3300</v>
+        <v>4800</v>
       </c>
       <c r="H17" s="3">
-        <v>5500</v>
+        <v>2700</v>
       </c>
       <c r="I17" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J17" s="3">
         <v>6000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2900</v>
-      </c>
-      <c r="L17" s="3">
-        <v>3300</v>
       </c>
       <c r="M17" s="3">
         <v>3300</v>
       </c>
       <c r="N17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O17" s="3">
         <v>4400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>600</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-4900</v>
+        <v>-2400</v>
       </c>
       <c r="E18" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F18" s="3">
         <v>800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-2400</v>
-      </c>
       <c r="H18" s="3">
-        <v>-4900</v>
+        <v>-2300</v>
       </c>
       <c r="I18" s="3">
-        <v>-4900</v>
+        <v>-9900</v>
       </c>
       <c r="J18" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,28 +1377,29 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1397,64 +1431,67 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2200</v>
       </c>
-      <c r="H21" s="3">
-        <v>-4700</v>
-      </c>
       <c r="I21" s="3">
-        <v>-4700</v>
+        <v>-9800</v>
       </c>
       <c r="J21" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-2600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1400</v>
       </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
+      <c r="S21" s="3">
+        <v>0</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
@@ -1462,8 +1499,11 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1521,78 +1561,84 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2400</v>
       </c>
-      <c r="H23" s="3">
-        <v>-4900</v>
-      </c>
       <c r="I23" s="3">
-        <v>-4900</v>
+        <v>-10200</v>
       </c>
       <c r="J23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>-100</v>
@@ -1604,23 +1650,23 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1633,14 +1679,17 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6100</v>
+        <v>-2300</v>
       </c>
       <c r="E26" s="3">
-        <v>700</v>
+        <v>-6200</v>
       </c>
       <c r="F26" s="3">
-        <v>-3100</v>
+        <v>800</v>
       </c>
       <c r="G26" s="3">
-        <v>-2300</v>
+        <v>-3200</v>
       </c>
       <c r="H26" s="3">
-        <v>-4900</v>
+        <v>-2400</v>
       </c>
       <c r="I26" s="3">
-        <v>-4900</v>
+        <v>-10200</v>
       </c>
       <c r="J26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-6100</v>
+        <v>-2300</v>
       </c>
       <c r="E27" s="3">
-        <v>700</v>
+        <v>-6200</v>
       </c>
       <c r="F27" s="3">
-        <v>-3100</v>
+        <v>800</v>
       </c>
       <c r="G27" s="3">
-        <v>-2300</v>
+        <v>-3200</v>
       </c>
       <c r="H27" s="3">
-        <v>-4900</v>
+        <v>-2400</v>
       </c>
       <c r="I27" s="3">
-        <v>-4900</v>
+        <v>-10200</v>
       </c>
       <c r="J27" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>100</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,31 +1933,34 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,28 +2119,31 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2105,73 +2175,79 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-6100</v>
+        <v>-2200</v>
       </c>
       <c r="E33" s="3">
-        <v>700</v>
+        <v>-6200</v>
       </c>
       <c r="F33" s="3">
-        <v>-3100</v>
+        <v>800</v>
       </c>
       <c r="G33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="H33" s="3">
         <v>-2300</v>
       </c>
-      <c r="H33" s="3">
-        <v>-4900</v>
-      </c>
       <c r="I33" s="3">
-        <v>-4900</v>
+        <v>-9900</v>
       </c>
       <c r="J33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>100</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-6100</v>
+        <v>-2200</v>
       </c>
       <c r="E35" s="3">
-        <v>700</v>
+        <v>-6200</v>
       </c>
       <c r="F35" s="3">
-        <v>-3100</v>
+        <v>800</v>
       </c>
       <c r="G35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="H35" s="3">
         <v>-2300</v>
       </c>
-      <c r="H35" s="3">
-        <v>-4900</v>
-      </c>
       <c r="I35" s="3">
-        <v>-4900</v>
+        <v>-9900</v>
       </c>
       <c r="J35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>100</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E38" s="2">
         <v>45351</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45260</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45169</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45077</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44985</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44895</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44804</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44712</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44620</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44530</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44439</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44347</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44255</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44165</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43524</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43434</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,47 +2484,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>600</v>
       </c>
-      <c r="F41" s="3">
-        <v>2400</v>
-      </c>
       <c r="G41" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H41" s="3">
         <v>1100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2457,8 +2544,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2504,8 +2594,8 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
+      <c r="R42" s="3">
+        <v>0</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
@@ -2516,47 +2606,50 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>600</v>
-      </c>
-      <c r="H43" s="3">
-        <v>700</v>
       </c>
       <c r="I43" s="3">
         <v>700</v>
       </c>
       <c r="J43" s="3">
+        <v>700</v>
+      </c>
+      <c r="K43" s="3">
         <v>800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2575,47 +2668,50 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>1800</v>
       </c>
       <c r="I44" s="3">
         <v>1900</v>
       </c>
       <c r="J44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K44" s="3">
         <v>1500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1400</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2634,47 +2730,50 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="E45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F45" s="3">
         <v>2100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,47 +2792,50 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="E46" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F46" s="3">
         <v>5500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6200</v>
       </c>
-      <c r="G46" s="3">
-        <v>4400</v>
-      </c>
       <c r="H46" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I46" s="3">
         <v>6100</v>
       </c>
-      <c r="I46" s="3">
-        <v>4700</v>
-      </c>
       <c r="J46" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K46" s="3">
         <v>8500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15500</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2752,13 +2854,16 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
         <v>100</v>
@@ -2773,25 +2878,25 @@
         <v>100</v>
       </c>
       <c r="I47" s="3">
+        <v>100</v>
+      </c>
+      <c r="J47" s="3">
         <v>2000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>1900</v>
       </c>
       <c r="K47" s="3">
         <v>1900</v>
       </c>
       <c r="L47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M47" s="3">
         <v>1500</v>
-      </c>
-      <c r="M47" s="3">
-        <v>2100</v>
       </c>
       <c r="N47" s="3">
         <v>2100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>2100</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -2805,37 +2910,40 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3200</v>
+        <v>2000</v>
       </c>
       <c r="E48" s="3">
         <v>3300</v>
       </c>
       <c r="F48" s="3">
-        <v>3400</v>
+        <v>3300</v>
       </c>
       <c r="G48" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="H48" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I48" s="3">
         <v>3300</v>
       </c>
-      <c r="I48" s="3">
-        <v>3400</v>
-      </c>
       <c r="J48" s="3">
-        <v>3300</v>
+        <v>3500</v>
       </c>
       <c r="K48" s="3">
         <v>3300</v>
@@ -2844,13 +2952,13 @@
         <v>3300</v>
       </c>
       <c r="M48" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="N48" s="3">
         <v>3100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
+      <c r="O48" s="3">
+        <v>3100</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
@@ -2870,16 +2978,19 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4600</v>
+        <v>3900</v>
       </c>
       <c r="E49" s="3">
-        <v>7800</v>
+        <v>4700</v>
       </c>
       <c r="F49" s="3">
         <v>7800</v>
@@ -2888,28 +2999,28 @@
         <v>7800</v>
       </c>
       <c r="H49" s="3">
-        <v>7800</v>
+        <v>7900</v>
       </c>
       <c r="I49" s="3">
         <v>7900</v>
       </c>
       <c r="J49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K49" s="3">
         <v>7600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7400</v>
-      </c>
-      <c r="M49" s="3">
-        <v>7500</v>
       </c>
       <c r="N49" s="3">
         <v>7500</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>7500</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
@@ -2923,14 +3034,17 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3164,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3059,10 +3179,10 @@
         <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
+        <v>100</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -3070,8 +3190,8 @@
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3085,8 +3205,8 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -3100,14 +3220,17 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,47 +3288,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>15500</v>
+        <v>12600</v>
       </c>
       <c r="E54" s="3">
-        <v>16700</v>
+        <v>15700</v>
       </c>
       <c r="F54" s="3">
+        <v>16800</v>
+      </c>
+      <c r="G54" s="3">
+        <v>17700</v>
+      </c>
+      <c r="H54" s="3">
+        <v>16100</v>
+      </c>
+      <c r="I54" s="3">
         <v>17500</v>
       </c>
-      <c r="G54" s="3">
-        <v>16000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>17300</v>
-      </c>
-      <c r="I54" s="3">
-        <v>18000</v>
-      </c>
       <c r="J54" s="3">
+        <v>18200</v>
+      </c>
+      <c r="K54" s="3">
         <v>21200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>24500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>28200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,47 +3400,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1100</v>
       </c>
       <c r="H57" s="3">
         <v>1100</v>
       </c>
       <c r="I57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J57" s="3">
         <v>1600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>500</v>
       </c>
       <c r="K57" s="3">
         <v>500</v>
       </c>
       <c r="L57" s="3">
+        <v>500</v>
+      </c>
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3329,31 +3460,34 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
         <v>700</v>
-      </c>
-      <c r="E58" s="3">
-        <v>800</v>
       </c>
       <c r="F58" s="3">
         <v>800</v>
       </c>
       <c r="G58" s="3">
+        <v>800</v>
+      </c>
+      <c r="H58" s="3">
         <v>900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>600</v>
-      </c>
-      <c r="J58" s="3">
-        <v>500</v>
       </c>
       <c r="K58" s="3">
         <v>500</v>
@@ -3362,13 +3496,13 @@
         <v>500</v>
       </c>
       <c r="M58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N58" s="3">
         <v>400</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>400</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
@@ -3388,47 +3522,50 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1900</v>
+        <v>1100</v>
       </c>
       <c r="E59" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="F59" s="3">
         <v>1900</v>
       </c>
       <c r="G59" s="3">
-        <v>900</v>
+        <v>2000</v>
       </c>
       <c r="H59" s="3">
         <v>900</v>
       </c>
       <c r="I59" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="J59" s="3">
         <v>1100</v>
       </c>
       <c r="K59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>900</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3447,47 +3584,50 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E60" s="3">
         <v>3700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4400</v>
       </c>
-      <c r="F60" s="3">
-        <v>3500</v>
-      </c>
       <c r="G60" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H60" s="3">
         <v>2900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,47 +3646,50 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1400</v>
+        <v>800</v>
       </c>
       <c r="E61" s="3">
         <v>1400</v>
       </c>
       <c r="F61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G61" s="3">
         <v>1500</v>
       </c>
-      <c r="G61" s="3">
-        <v>1600</v>
-      </c>
       <c r="H61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I61" s="3">
         <v>1400</v>
-      </c>
-      <c r="I61" s="3">
-        <v>1500</v>
       </c>
       <c r="J61" s="3">
         <v>1500</v>
       </c>
       <c r="K61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L61" s="3">
         <v>1600</v>
-      </c>
-      <c r="L61" s="3">
-        <v>1700</v>
       </c>
       <c r="M61" s="3">
         <v>1700</v>
       </c>
       <c r="N61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O61" s="3">
         <v>1800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3565,28 +3708,31 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5800</v>
+        <v>6200</v>
       </c>
       <c r="E62" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>100</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
@@ -3603,8 +3749,8 @@
       <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
+      <c r="O62" s="3">
+        <v>100</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,37 +3956,40 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10900</v>
+        <v>9900</v>
       </c>
       <c r="E66" s="3">
-        <v>6400</v>
+        <v>11000</v>
       </c>
       <c r="F66" s="3">
-        <v>9100</v>
+        <v>6500</v>
       </c>
       <c r="G66" s="3">
-        <v>7000</v>
+        <v>9200</v>
       </c>
       <c r="H66" s="3">
-        <v>7600</v>
+        <v>7100</v>
       </c>
       <c r="I66" s="3">
-        <v>4800</v>
+        <v>7700</v>
       </c>
       <c r="J66" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K66" s="3">
         <v>3700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4200</v>
-      </c>
-      <c r="L66" s="3">
-        <v>3800</v>
       </c>
       <c r="M66" s="3">
         <v>3800</v>
@@ -3839,8 +3997,8 @@
       <c r="N66" s="3">
         <v>3800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
+      <c r="O66" s="3">
+        <v>3800</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
@@ -3860,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,47 +4290,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-34200</v>
+        <v>-36700</v>
       </c>
       <c r="E72" s="3">
-        <v>-28200</v>
+        <v>-34500</v>
       </c>
       <c r="F72" s="3">
-        <v>-29100</v>
+        <v>-28500</v>
       </c>
       <c r="G72" s="3">
-        <v>-26000</v>
+        <v>-29300</v>
       </c>
       <c r="H72" s="3">
-        <v>-24200</v>
+        <v>-26200</v>
       </c>
       <c r="I72" s="3">
-        <v>-19400</v>
+        <v>-24400</v>
       </c>
       <c r="J72" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="K72" s="3">
         <v>-14700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-12000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-11000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7100</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,47 +4538,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E76" s="3">
         <v>4700</v>
       </c>
-      <c r="E76" s="3">
-        <v>10300</v>
-      </c>
       <c r="F76" s="3">
-        <v>8400</v>
+        <v>10400</v>
       </c>
       <c r="G76" s="3">
+        <v>8500</v>
+      </c>
+      <c r="H76" s="3">
         <v>9000</v>
       </c>
-      <c r="H76" s="3">
-        <v>9700</v>
-      </c>
       <c r="I76" s="3">
-        <v>13200</v>
+        <v>9800</v>
       </c>
       <c r="J76" s="3">
+        <v>13300</v>
+      </c>
+      <c r="K76" s="3">
         <v>17500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24400</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4414,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45443</v>
+      </c>
+      <c r="E80" s="2">
         <v>45351</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45260</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45169</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45077</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44985</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44895</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44804</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44712</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44620</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44530</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44439</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44347</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44255</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44165</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43524</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43434</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-6100</v>
+        <v>-2200</v>
       </c>
       <c r="E81" s="3">
-        <v>700</v>
+        <v>-6200</v>
       </c>
       <c r="F81" s="3">
-        <v>-3100</v>
+        <v>800</v>
       </c>
       <c r="G81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="H81" s="3">
         <v>-2300</v>
       </c>
-      <c r="H81" s="3">
-        <v>-4900</v>
-      </c>
       <c r="I81" s="3">
-        <v>-4900</v>
+        <v>-9900</v>
       </c>
       <c r="J81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>100</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4640,7 +4839,7 @@
         <v>200</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
@@ -4655,7 +4854,7 @@
         <v>200</v>
       </c>
       <c r="N83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>100</v>
@@ -4666,8 +4865,8 @@
       <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>100</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
@@ -4678,8 +4877,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,56 +5187,59 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
-        <v>-3000</v>
-      </c>
       <c r="H89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M89" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="N89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="O89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P89" s="3">
         <v>-2400</v>
       </c>
-      <c r="I89" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5032,8 +5249,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,55 +5275,56 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-300</v>
       </c>
       <c r="I91" s="3">
         <v>-300</v>
       </c>
       <c r="J91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5114,8 +5335,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,55 +5459,58 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-400</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5291,8 +5521,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,56 +5793,59 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>4700</v>
+        <v>-400</v>
       </c>
       <c r="E100" s="3">
-        <v>1100</v>
+        <v>4800</v>
       </c>
       <c r="F100" s="3">
-        <v>3300</v>
+        <v>1200</v>
       </c>
       <c r="G100" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H100" s="3">
         <v>1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>26600</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5609,8 +5855,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5668,56 +5917,59 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
-        <v>-1800</v>
-      </c>
       <c r="F102" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="G102" s="3">
         <v>1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1900</v>
       </c>
-      <c r="H102" s="3">
-        <v>1800</v>
-      </c>
       <c r="I102" s="3">
-        <v>-3000</v>
+        <v>-1300</v>
       </c>
       <c r="J102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>25100</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5725,6 +5977,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>VMAR</t>
   </si>
@@ -656,147 +656,151 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E7" s="2">
         <v>45443</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45351</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45260</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45169</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45077</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44985</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44895</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44804</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44712</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44620</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44530</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44439</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44347</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44255</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44165</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43524</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43434</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E8" s="3">
+        <v>800</v>
+      </c>
+      <c r="F8" s="3">
         <v>500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>600</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L8" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M8" s="3">
         <v>1500</v>
       </c>
-      <c r="H8" s="3">
-        <v>400</v>
-      </c>
-      <c r="I8" s="3">
-        <v>400</v>
-      </c>
-      <c r="J8" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K8" s="3">
-        <v>2500</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>600</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>200</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -805,21 +809,24 @@
         <v>200</v>
       </c>
       <c r="T8" s="3">
+        <v>200</v>
+      </c>
+      <c r="U8" s="3">
         <v>700</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E9" s="3">
         <v>400</v>
@@ -828,117 +835,123 @@
         <v>400</v>
       </c>
       <c r="G9" s="3">
+        <v>400</v>
+      </c>
+      <c r="H9" s="3">
         <v>800</v>
       </c>
-      <c r="H9" s="3">
-        <v>300</v>
-      </c>
       <c r="I9" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="J9" s="3">
+        <v>600</v>
+      </c>
+      <c r="K9" s="3">
         <v>1000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>400</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
-        <v>100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>300</v>
-      </c>
-      <c r="G10" s="3">
-        <v>700</v>
-      </c>
-      <c r="H10" s="3">
-        <v>100</v>
-      </c>
-      <c r="I10" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J10" s="3">
-        <v>100</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1000</v>
-      </c>
-      <c r="P10" s="3">
-        <v>100</v>
       </c>
       <c r="Q10" s="3">
         <v>100</v>
       </c>
       <c r="R10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
         <v>100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,58 +974,59 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>600</v>
+      </c>
+      <c r="E12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="I12" s="3">
-        <v>3300</v>
-      </c>
       <c r="J12" s="3">
+        <v>500</v>
+      </c>
+      <c r="K12" s="3">
         <v>2700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1600</v>
       </c>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
       <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>-100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
       <c r="R12" s="3">
         <v>0</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
+      <c r="S12" s="3">
+        <v>0</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
@@ -1023,8 +1037,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,49 +1102,52 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>1900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1147,19 +1167,22 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
@@ -1168,7 +1191,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
@@ -1177,7 +1200,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1186,11 +1209,11 @@
         <v>0</v>
       </c>
       <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
         <v>100</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1203,14 +1226,17 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,8 +1256,9 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1239,123 +1266,129 @@
         <v>2900</v>
       </c>
       <c r="E17" s="3">
-        <v>5500</v>
+        <v>2800</v>
       </c>
       <c r="F17" s="3">
-        <v>-100</v>
+        <v>2900</v>
       </c>
       <c r="G17" s="3">
-        <v>4800</v>
+        <v>3900</v>
       </c>
       <c r="H17" s="3">
-        <v>2700</v>
+        <v>5100</v>
       </c>
       <c r="I17" s="3">
-        <v>10300</v>
+        <v>4400</v>
       </c>
       <c r="J17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K17" s="3">
         <v>6000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2900</v>
-      </c>
-      <c r="M17" s="3">
-        <v>3300</v>
       </c>
       <c r="N17" s="3">
         <v>3300</v>
       </c>
       <c r="O17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P17" s="3">
         <v>4400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2400</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>800</v>
       </c>
       <c r="G18" s="3">
         <v>-3200</v>
       </c>
       <c r="H18" s="3">
-        <v>-2300</v>
+        <v>-3500</v>
       </c>
       <c r="I18" s="3">
-        <v>-9900</v>
+        <v>-3500</v>
       </c>
       <c r="J18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K18" s="3">
         <v>-5000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,31 +1411,32 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-2600</v>
       </c>
       <c r="E20" s="3">
-        <v>-1200</v>
+        <v>400</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>600</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-3900</v>
       </c>
       <c r="H20" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="I20" s="3">
-        <v>-300</v>
+        <v>-1100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1434,67 +1468,70 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2200</v>
       </c>
-      <c r="E21" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-9800</v>
-      </c>
       <c r="J21" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-4800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1400</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
+      <c r="T21" s="3">
+        <v>0</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
@@ -1502,19 +1539,22 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1523,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1564,112 +1604,118 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G23" s="3">
+        <v>700</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I23" s="3">
         <v>-2400</v>
       </c>
-      <c r="E23" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="F23" s="3">
-        <v>700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-10200</v>
-      </c>
       <c r="J23" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-5000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1682,14 +1728,17 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1799,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G26" s="3">
+        <v>800</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2300</v>
       </c>
-      <c r="E26" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="F26" s="3">
-        <v>800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-10200</v>
-      </c>
       <c r="J26" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-5000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G27" s="3">
+        <v>800</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2300</v>
       </c>
-      <c r="E27" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="F27" s="3">
-        <v>800</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-10200</v>
-      </c>
       <c r="J27" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>100</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,34 +1994,37 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>100</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>300</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,31 +2189,34 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="E32" s="3">
-        <v>1200</v>
+        <v>-400</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>-600</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>3900</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I32" s="3">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2178,76 +2248,82 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2300</v>
       </c>
-      <c r="I33" s="3">
-        <v>-9900</v>
-      </c>
       <c r="J33" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>100</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2300</v>
       </c>
-      <c r="I35" s="3">
-        <v>-9900</v>
-      </c>
       <c r="J35" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>100</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E38" s="2">
         <v>45443</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45351</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45260</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45169</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45077</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44985</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44895</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44804</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44712</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44620</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44530</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44439</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44347</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44255</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44165</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43524</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43434</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,50 +2571,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,8 +2634,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2597,8 +2687,8 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
+      <c r="S42" s="3">
+        <v>0</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
@@ -2609,50 +2699,53 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>300</v>
       </c>
       <c r="F43" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G43" s="3">
         <v>500</v>
       </c>
       <c r="H43" s="3">
+        <v>500</v>
+      </c>
+      <c r="I43" s="3">
         <v>600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
+        <v>800</v>
+      </c>
+      <c r="K43" s="3">
         <v>700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
+        <v>800</v>
+      </c>
+      <c r="M43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N43" s="3">
+        <v>800</v>
+      </c>
+      <c r="O43" s="3">
         <v>700</v>
       </c>
-      <c r="K43" s="3">
-        <v>800</v>
-      </c>
-      <c r="L43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="M43" s="3">
-        <v>800</v>
-      </c>
-      <c r="N43" s="3">
-        <v>700</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2671,50 +2764,53 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E44" s="3">
         <v>4000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>1900</v>
       </c>
       <c r="J44" s="3">
         <v>1900</v>
       </c>
       <c r="K44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L44" s="3">
         <v>1500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1400</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2733,50 +2829,53 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
+        <v>900</v>
+      </c>
+      <c r="L45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="N45" s="3">
         <v>2100</v>
       </c>
-      <c r="E45" s="3">
-        <v>2900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="I45" s="3">
-        <v>500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="N45" s="3">
-        <v>800</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,50 +2894,53 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E46" s="3">
         <v>6600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5500</v>
       </c>
-      <c r="G46" s="3">
-        <v>6200</v>
-      </c>
       <c r="H46" s="3">
+        <v>6300</v>
+      </c>
+      <c r="I46" s="3">
         <v>4500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15500</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,49 +2959,52 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>100</v>
-      </c>
-      <c r="H47" s="3">
-        <v>100</v>
-      </c>
-      <c r="I47" s="3">
-        <v>100</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>2000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>1900</v>
       </c>
       <c r="L47" s="3">
         <v>1900</v>
       </c>
       <c r="M47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N47" s="3">
         <v>1500</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2100</v>
       </c>
       <c r="O47" s="3">
         <v>2100</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>2100</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
@@ -2913,40 +3018,43 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E48" s="3">
         <v>2000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>3300</v>
       </c>
       <c r="F48" s="3">
         <v>3300</v>
       </c>
       <c r="G48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H48" s="3">
         <v>3500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3500</v>
-      </c>
-      <c r="K48" s="3">
-        <v>3300</v>
       </c>
       <c r="L48" s="3">
         <v>3300</v>
@@ -2955,13 +3063,13 @@
         <v>3300</v>
       </c>
       <c r="N48" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="O48" s="3">
         <v>3100</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3">
+        <v>3100</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
@@ -2981,19 +3089,22 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>600</v>
+      </c>
+      <c r="E49" s="3">
         <v>3900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4700</v>
-      </c>
-      <c r="F49" s="3">
-        <v>7800</v>
       </c>
       <c r="G49" s="3">
         <v>7800</v>
@@ -3008,22 +3119,22 @@
         <v>7900</v>
       </c>
       <c r="K49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="L49" s="3">
         <v>7600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7400</v>
-      </c>
-      <c r="N49" s="3">
-        <v>7500</v>
       </c>
       <c r="O49" s="3">
         <v>7500</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>7500</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -3037,14 +3148,17 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,16 +3284,19 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -3184,17 +3304,17 @@
       <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="H52" s="3">
+        <v>100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3208,8 +3328,8 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -3223,14 +3343,17 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,50 +3414,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E54" s="3">
         <v>12600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15700</v>
       </c>
-      <c r="F54" s="3">
-        <v>16800</v>
-      </c>
       <c r="G54" s="3">
-        <v>17700</v>
+        <v>16900</v>
       </c>
       <c r="H54" s="3">
+        <v>17800</v>
+      </c>
+      <c r="I54" s="3">
         <v>16100</v>
       </c>
-      <c r="I54" s="3">
-        <v>17500</v>
-      </c>
       <c r="J54" s="3">
+        <v>17400</v>
+      </c>
+      <c r="K54" s="3">
         <v>18200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>28200</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3479,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,50 +3531,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1100</v>
       </c>
       <c r="I57" s="3">
         <v>1100</v>
       </c>
       <c r="J57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K57" s="3">
         <v>1600</v>
-      </c>
-      <c r="K57" s="3">
-        <v>500</v>
       </c>
       <c r="L57" s="3">
         <v>500</v>
       </c>
       <c r="M57" s="3">
+        <v>500</v>
+      </c>
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,34 +3594,37 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>200</v>
+      </c>
+      <c r="E58" s="3">
         <v>400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>700</v>
-      </c>
-      <c r="F58" s="3">
-        <v>800</v>
       </c>
       <c r="G58" s="3">
         <v>800</v>
       </c>
       <c r="H58" s="3">
+        <v>800</v>
+      </c>
+      <c r="I58" s="3">
         <v>900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>500</v>
       </c>
       <c r="L58" s="3">
         <v>500</v>
@@ -3499,13 +3633,13 @@
         <v>500</v>
       </c>
       <c r="N58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O58" s="3">
         <v>400</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3">
+        <v>400</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
@@ -3525,50 +3659,53 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="F59" s="3">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="G59" s="3">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="H59" s="3">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="I59" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="J59" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="K59" s="3">
         <v>1100</v>
       </c>
       <c r="L59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M59" s="3">
         <v>1500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>900</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,50 +3724,53 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3649,50 +3789,53 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>400</v>
+      </c>
+      <c r="E61" s="3">
         <v>800</v>
-      </c>
-      <c r="E61" s="3">
-        <v>1400</v>
       </c>
       <c r="F61" s="3">
         <v>1400</v>
       </c>
       <c r="G61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H61" s="3">
         <v>1500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1400</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1500</v>
       </c>
       <c r="K61" s="3">
         <v>1500</v>
       </c>
       <c r="L61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M61" s="3">
         <v>1600</v>
-      </c>
-      <c r="M61" s="3">
-        <v>1700</v>
       </c>
       <c r="N61" s="3">
         <v>1700</v>
       </c>
       <c r="O61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P61" s="3">
         <v>1800</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3711,31 +3854,34 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6200</v>
+        <v>1600</v>
       </c>
       <c r="E62" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F62" s="3">
         <v>5900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4100</v>
       </c>
-      <c r="H62" s="3">
-        <v>2500</v>
-      </c>
       <c r="I62" s="3">
-        <v>2900</v>
+        <v>2400</v>
       </c>
       <c r="J62" s="3">
-        <v>100</v>
+        <v>2800</v>
       </c>
       <c r="K62" s="3">
         <v>100</v>
@@ -3752,8 +3898,8 @@
       <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
+      <c r="P62" s="3">
+        <v>100</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
@@ -3773,8 +3919,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,40 +4114,43 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>9900</v>
+        <v>6200</v>
       </c>
       <c r="E66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F66" s="3">
         <v>11000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4200</v>
-      </c>
-      <c r="M66" s="3">
-        <v>3800</v>
       </c>
       <c r="N66" s="3">
         <v>3800</v>
@@ -4000,8 +4158,8 @@
       <c r="O66" s="3">
         <v>3800</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
+      <c r="P66" s="3">
+        <v>3800</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
@@ -4021,8 +4179,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,50 +4464,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-36700</v>
+        <v>-48600</v>
       </c>
       <c r="E72" s="3">
-        <v>-34500</v>
+        <v>-45400</v>
       </c>
       <c r="F72" s="3">
-        <v>-28500</v>
+        <v>-43400</v>
       </c>
       <c r="G72" s="3">
-        <v>-29300</v>
+        <v>-37200</v>
       </c>
       <c r="H72" s="3">
-        <v>-26200</v>
+        <v>-38100</v>
       </c>
       <c r="I72" s="3">
-        <v>-24400</v>
+        <v>-34800</v>
       </c>
       <c r="J72" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-19600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-14700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-12000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-11000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7100</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4355,8 +4529,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,50 +4724,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>24400</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4603,8 +4789,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45535</v>
+      </c>
+      <c r="E80" s="2">
         <v>45443</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45351</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45260</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45169</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45077</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44985</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44895</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44804</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44712</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44620</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44530</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44439</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44347</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44255</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44165</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43524</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43434</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2300</v>
       </c>
-      <c r="I81" s="3">
-        <v>-9900</v>
-      </c>
       <c r="J81" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>100</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,8 +5016,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4836,10 +5035,10 @@
         <v>200</v>
       </c>
       <c r="H83" s="3">
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
         <v>200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>400</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
@@ -4857,7 +5056,7 @@
         <v>200</v>
       </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
@@ -4868,8 +5067,8 @@
       <c r="R83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>100</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
@@ -4880,8 +5079,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,59 +5404,62 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3100</v>
       </c>
-      <c r="I89" s="3">
-        <v>-5300</v>
-      </c>
       <c r="J89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-2900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5252,8 +5469,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,58 +5496,59 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5338,8 +5559,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,58 +5689,61 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-200</v>
       </c>
       <c r="I94" s="3">
         <v>-200</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5524,8 +5754,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,31 +5781,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,59 +6039,62 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="I100" s="3">
-        <v>4200</v>
-      </c>
       <c r="J100" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>26600</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5858,31 +6104,34 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5920,59 +6169,62 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1900</v>
       </c>
-      <c r="I102" s="3">
-        <v>-1300</v>
-      </c>
       <c r="J102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K102" s="3">
         <v>-3100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>25100</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5980,6 +6232,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>VMAR</t>
   </si>
@@ -656,154 +656,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E7" s="2">
         <v>45535</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45443</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45351</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45260</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45169</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45077</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44985</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44895</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44804</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44712</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44620</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44530</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44439</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44347</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44255</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44165</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43524</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43434</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="E8" s="3">
         <v>800</v>
       </c>
       <c r="F8" s="3">
+        <v>800</v>
+      </c>
+      <c r="G8" s="3">
         <v>500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>600</v>
-      </c>
-      <c r="R8" s="3">
-        <v>200</v>
       </c>
       <c r="S8" s="3">
         <v>200</v>
@@ -812,24 +815,27 @@
         <v>200</v>
       </c>
       <c r="U8" s="3">
+        <v>200</v>
+      </c>
+      <c r="V8" s="3">
         <v>700</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
         <v>500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>400</v>
       </c>
       <c r="F9" s="3">
         <v>400</v>
@@ -838,120 +844,126 @@
         <v>400</v>
       </c>
       <c r="H9" s="3">
+        <v>400</v>
+      </c>
+      <c r="I9" s="3">
         <v>800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>400</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3">
         <v>300</v>
       </c>
       <c r="F10" s="3">
+        <v>300</v>
+      </c>
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
       <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>100</v>
       </c>
       <c r="R10" s="3">
         <v>100</v>
       </c>
       <c r="S10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <v>100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>300</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,61 +987,62 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
         <v>600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1600</v>
       </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
       <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>-100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
       <c r="S12" s="3">
         <v>0</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
+      <c r="T12" s="3">
+        <v>0</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
@@ -1040,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,52 +1121,55 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>3300</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>1900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1170,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1179,22 +1201,22 @@
         <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
       </c>
       <c r="I15" s="3">
+        <v>100</v>
+      </c>
+      <c r="J15" s="3">
         <v>200</v>
-      </c>
-      <c r="J15" s="3">
-        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1203,7 +1225,7 @@
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1212,11 +1234,11 @@
         <v>0</v>
       </c>
       <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
         <v>100</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1229,14 +1251,17 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E17" s="3">
         <v>2900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2900</v>
-      </c>
-      <c r="N17" s="3">
-        <v>3300</v>
       </c>
       <c r="O17" s="3">
         <v>3300</v>
       </c>
       <c r="P17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q17" s="3">
         <v>4400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>600</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-3500</v>
       </c>
       <c r="I18" s="3">
         <v>-3500</v>
       </c>
       <c r="J18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,35 +1444,36 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2600</v>
+        <v>-1000</v>
       </c>
       <c r="E20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1471,70 +1504,73 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>600</v>
+        <v>-1000</v>
       </c>
       <c r="E21" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1400</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
+      <c r="U21" s="3">
+        <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
@@ -1542,34 +1578,37 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
       <c r="I22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>100</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1607,73 +1646,79 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1681,44 +1726,44 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
         <v>-100</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1731,14 +1776,17 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>100</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>100</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2023,11 +2083,11 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,35 +2258,38 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2600</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2251,79 +2320,85 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>100</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>100</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E38" s="2">
         <v>45535</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45443</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45351</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45260</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45169</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45077</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44985</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44895</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44804</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44712</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44620</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44530</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44439</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44347</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44255</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44165</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43524</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43434</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,53 +2657,54 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2637,8 +2723,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2690,8 +2779,8 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
+      <c r="T42" s="3">
+        <v>0</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
@@ -2702,53 +2791,56 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
-      </c>
-      <c r="E43" s="3">
-        <v>300</v>
       </c>
       <c r="F43" s="3">
         <v>300</v>
       </c>
       <c r="G43" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H43" s="3">
         <v>500</v>
       </c>
       <c r="I43" s="3">
+        <v>500</v>
+      </c>
+      <c r="J43" s="3">
         <v>600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>300</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2767,53 +2859,56 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="E44" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F44" s="3">
         <v>4000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2000</v>
-      </c>
-      <c r="J44" s="3">
-        <v>1900</v>
       </c>
       <c r="K44" s="3">
         <v>1900</v>
       </c>
       <c r="L44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M44" s="3">
         <v>1500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1400</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2832,16 +2927,19 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
@@ -2859,26 +2957,26 @@
         <v>0</v>
       </c>
       <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2897,53 +2995,56 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E46" s="3">
         <v>6400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15500</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2962,8 +3063,11 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2988,26 +3092,26 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>2000</v>
-      </c>
-      <c r="L47" s="3">
-        <v>1900</v>
       </c>
       <c r="M47" s="3">
         <v>1900</v>
       </c>
       <c r="N47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O47" s="3">
         <v>1500</v>
-      </c>
-      <c r="O47" s="3">
-        <v>2100</v>
       </c>
       <c r="P47" s="3">
         <v>2100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>2100</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -3021,43 +3125,46 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>3300</v>
       </c>
       <c r="G48" s="3">
         <v>3300</v>
       </c>
       <c r="H48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I48" s="3">
         <v>3500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>3300</v>
       </c>
       <c r="M48" s="3">
         <v>3300</v>
@@ -3066,13 +3173,13 @@
         <v>3300</v>
       </c>
       <c r="O48" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="P48" s="3">
         <v>3100</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
+      <c r="Q48" s="3">
+        <v>3100</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
@@ -3092,8 +3199,11 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3101,16 +3211,16 @@
         <v>600</v>
       </c>
       <c r="E49" s="3">
+        <v>600</v>
+      </c>
+      <c r="F49" s="3">
         <v>3900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7800</v>
-      </c>
-      <c r="H49" s="3">
-        <v>7900</v>
       </c>
       <c r="I49" s="3">
         <v>7900</v>
@@ -3122,22 +3232,22 @@
         <v>7900</v>
       </c>
       <c r="L49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="M49" s="3">
         <v>7600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7400</v>
-      </c>
-      <c r="O49" s="3">
-        <v>7500</v>
       </c>
       <c r="P49" s="3">
         <v>7500</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>7500</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -3151,14 +3261,17 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3299,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
@@ -3313,11 +3432,11 @@
       <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3331,8 +3450,8 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>0</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
@@ -3346,14 +3465,17 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,53 +3539,56 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E54" s="3">
         <v>8500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>28200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3482,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,53 +3661,54 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3300</v>
+        <v>1200</v>
       </c>
       <c r="E57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1100</v>
       </c>
       <c r="J57" s="3">
         <v>1100</v>
       </c>
       <c r="K57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L57" s="3">
         <v>1600</v>
-      </c>
-      <c r="L57" s="3">
-        <v>500</v>
       </c>
       <c r="M57" s="3">
         <v>500</v>
       </c>
       <c r="N57" s="3">
+        <v>500</v>
+      </c>
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3597,8 +3727,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3606,28 +3739,28 @@
         <v>200</v>
       </c>
       <c r="E58" s="3">
+        <v>200</v>
+      </c>
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>700</v>
-      </c>
-      <c r="G58" s="3">
-        <v>800</v>
       </c>
       <c r="H58" s="3">
         <v>800</v>
       </c>
       <c r="I58" s="3">
+        <v>800</v>
+      </c>
+      <c r="J58" s="3">
         <v>900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>600</v>
-      </c>
-      <c r="L58" s="3">
-        <v>500</v>
       </c>
       <c r="M58" s="3">
         <v>500</v>
@@ -3636,13 +3769,13 @@
         <v>500</v>
       </c>
       <c r="O58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P58" s="3">
         <v>400</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>400</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
@@ -3662,53 +3795,56 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="E59" s="3">
         <v>700</v>
       </c>
       <c r="F59" s="3">
+        <v>700</v>
+      </c>
+      <c r="G59" s="3">
         <v>1400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1500</v>
       </c>
       <c r="H59" s="3">
         <v>1500</v>
       </c>
       <c r="I59" s="3">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="J59" s="3">
         <v>700</v>
       </c>
       <c r="K59" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="L59" s="3">
         <v>1100</v>
       </c>
       <c r="M59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>900</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,53 +3863,56 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E60" s="3">
         <v>4200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3792,53 +3931,56 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
         <v>400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>800</v>
-      </c>
-      <c r="F61" s="3">
-        <v>1400</v>
       </c>
       <c r="G61" s="3">
         <v>1400</v>
       </c>
       <c r="H61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I61" s="3">
         <v>1500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1400</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1500</v>
       </c>
       <c r="L61" s="3">
         <v>1500</v>
       </c>
       <c r="M61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N61" s="3">
         <v>1600</v>
-      </c>
-      <c r="N61" s="3">
-        <v>1700</v>
       </c>
       <c r="O61" s="3">
         <v>1700</v>
       </c>
       <c r="P61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q61" s="3">
         <v>1800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3857,34 +3999,37 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3">
         <v>1600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2800</v>
-      </c>
-      <c r="K62" s="3">
-        <v>100</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
@@ -3901,8 +4046,8 @@
       <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="Q62" s="3">
+        <v>100</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3922,8 +4067,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,43 +4271,46 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E66" s="3">
         <v>6200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4200</v>
-      </c>
-      <c r="N66" s="3">
-        <v>3800</v>
       </c>
       <c r="O66" s="3">
         <v>3800</v>
@@ -4161,8 +4318,8 @@
       <c r="P66" s="3">
         <v>3800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
+      <c r="Q66" s="3">
+        <v>3800</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
@@ -4182,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,53 +4637,56 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-48600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-45400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-43400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-37200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-38100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-34800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-32500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-19600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-14700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-12000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,53 +4909,56 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>24400</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E80" s="2">
         <v>45535</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45443</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45351</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45260</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45169</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45077</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44985</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44895</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44804</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44712</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44620</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44530</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44439</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44347</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44255</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44165</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43524</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43434</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>100</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5026,7 +5224,7 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -5035,10 +5233,10 @@
         <v>200</v>
       </c>
       <c r="H83" s="3">
+        <v>200</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>200</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
@@ -5059,7 +5257,7 @@
         <v>200</v>
       </c>
       <c r="P83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
@@ -5070,8 +5268,8 @@
       <c r="S83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>100</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
@@ -5082,8 +5280,11 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,62 +5620,65 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1500</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5472,8 +5688,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,61 +5716,62 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-200</v>
       </c>
       <c r="F91" s="3">
         <v>-200</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-200</v>
       </c>
       <c r="K91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5562,8 +5782,11 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,8 +5918,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5701,52 +5930,52 @@
         <v>0</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -5757,8 +5986,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5808,8 +6041,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5847,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,62 +6284,65 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E100" s="3">
         <v>200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>26600</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6107,8 +6352,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6133,8 +6381,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6172,62 +6420,65 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>25100</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6235,6 +6486,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
   <si>
     <t>VMAR</t>
   </si>
@@ -656,160 +656,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E7" s="2">
         <v>45626</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45535</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45443</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45351</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45260</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45169</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45077</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44985</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44895</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44804</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44712</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44620</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44530</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44439</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44347</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44255</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44165</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43524</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43434</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
-      </c>
-      <c r="E8" s="3">
-        <v>800</v>
       </c>
       <c r="F8" s="3">
         <v>800</v>
       </c>
       <c r="G8" s="3">
+        <v>800</v>
+      </c>
+      <c r="H8" s="3">
         <v>500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>600</v>
-      </c>
-      <c r="S8" s="3">
-        <v>200</v>
       </c>
       <c r="T8" s="3">
         <v>200</v>
@@ -818,16 +822,19 @@
         <v>200</v>
       </c>
       <c r="V8" s="3">
+        <v>200</v>
+      </c>
+      <c r="W8" s="3">
         <v>700</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -835,10 +842,10 @@
         <v>100</v>
       </c>
       <c r="E9" s="3">
+        <v>100</v>
+      </c>
+      <c r="F9" s="3">
         <v>500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>400</v>
       </c>
       <c r="G9" s="3">
         <v>400</v>
@@ -847,55 +854,58 @@
         <v>400</v>
       </c>
       <c r="I9" s="3">
+        <v>400</v>
+      </c>
+      <c r="J9" s="3">
         <v>800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>400</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -903,67 +913,70 @@
         <v>0</v>
       </c>
       <c r="E10" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3">
         <v>300</v>
       </c>
       <c r="G10" s="3">
+        <v>300</v>
+      </c>
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
       <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1000</v>
-      </c>
-      <c r="R10" s="3">
-        <v>100</v>
       </c>
       <c r="S10" s="3">
         <v>100</v>
       </c>
       <c r="T10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U10" s="3">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3">
         <v>100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>300</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,64 +1001,65 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1600</v>
       </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
       <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>-100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3">
-        <v>0</v>
-      </c>
       <c r="T12" s="3">
         <v>0</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
+      <c r="U12" s="3">
+        <v>0</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,55 +1141,58 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>4600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3100</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>1900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1204,22 +1227,22 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>100</v>
       </c>
       <c r="J15" s="3">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
         <v>200</v>
-      </c>
-      <c r="K15" s="3">
-        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
@@ -1228,7 +1251,7 @@
         <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1237,11 +1260,11 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
         <v>100</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
@@ -1254,14 +1277,17 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2900</v>
-      </c>
-      <c r="O17" s="3">
-        <v>3300</v>
       </c>
       <c r="P17" s="3">
         <v>3300</v>
       </c>
       <c r="Q17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="R17" s="3">
         <v>4400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>600</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-3500</v>
       </c>
       <c r="J18" s="3">
         <v>-3500</v>
       </c>
       <c r="K18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="L18" s="3">
         <v>-2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,38 +1478,39 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1507,73 +1541,76 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1400</v>
       </c>
-      <c r="U21" s="3">
-        <v>0</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
+      <c r="V21" s="3">
+        <v>0</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
@@ -1581,8 +1618,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1596,22 +1636,22 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
       <c r="J22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
       </c>
       <c r="L22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1649,76 +1689,82 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>100</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1729,44 +1775,44 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
         <v>-100</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1779,14 +1825,17 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>100</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>100</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2086,11 +2147,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,38 +2328,41 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2323,82 +2393,88 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>100</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>100</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E38" s="2">
         <v>45626</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45535</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45443</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45351</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45260</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45169</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45077</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44985</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44895</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44804</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44712</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44620</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44530</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44439</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44347</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44255</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44165</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43524</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43434</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,56 +2744,57 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E41" s="3">
         <v>700</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,8 +2813,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2782,8 +2872,8 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
+      <c r="U42" s="3">
+        <v>0</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
@@ -2794,8 +2884,11 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2803,47 +2896,47 @@
         <v>200</v>
       </c>
       <c r="E43" s="3">
+        <v>200</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
-      </c>
-      <c r="F43" s="3">
-        <v>300</v>
       </c>
       <c r="G43" s="3">
         <v>300</v>
       </c>
       <c r="H43" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I43" s="3">
         <v>500</v>
       </c>
       <c r="J43" s="3">
+        <v>500</v>
+      </c>
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>300</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2862,56 +2955,59 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E44" s="3">
         <v>4500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2000</v>
-      </c>
-      <c r="K44" s="3">
-        <v>1900</v>
       </c>
       <c r="L44" s="3">
         <v>1900</v>
       </c>
       <c r="M44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N44" s="3">
         <v>1500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1400</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,19 +3026,22 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
         <v>0</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
@@ -2960,26 +3059,26 @@
         <v>0</v>
       </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2998,56 +3097,59 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E46" s="3">
         <v>7500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15500</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3066,8 +3168,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3095,26 +3200,26 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>2000</v>
-      </c>
-      <c r="M47" s="3">
-        <v>1900</v>
       </c>
       <c r="N47" s="3">
         <v>1900</v>
       </c>
       <c r="O47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P47" s="3">
         <v>1500</v>
-      </c>
-      <c r="P47" s="3">
-        <v>2100</v>
       </c>
       <c r="Q47" s="3">
         <v>2100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>2100</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -3128,46 +3233,49 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>3300</v>
       </c>
       <c r="H48" s="3">
         <v>3300</v>
       </c>
       <c r="I48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="J48" s="3">
         <v>3500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3500</v>
-      </c>
-      <c r="M48" s="3">
-        <v>3300</v>
       </c>
       <c r="N48" s="3">
         <v>3300</v>
@@ -3176,13 +3284,13 @@
         <v>3300</v>
       </c>
       <c r="P48" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="Q48" s="3">
         <v>3100</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
+      <c r="R48" s="3">
+        <v>3100</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
@@ -3202,8 +3310,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3214,16 +3325,16 @@
         <v>600</v>
       </c>
       <c r="F49" s="3">
+        <v>600</v>
+      </c>
+      <c r="G49" s="3">
         <v>3900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7800</v>
-      </c>
-      <c r="I49" s="3">
-        <v>7900</v>
       </c>
       <c r="J49" s="3">
         <v>7900</v>
@@ -3235,22 +3346,22 @@
         <v>7900</v>
       </c>
       <c r="M49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="N49" s="3">
         <v>7600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7400</v>
-      </c>
-      <c r="P49" s="3">
-        <v>7500</v>
       </c>
       <c r="Q49" s="3">
         <v>7500</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>7500</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -3264,14 +3375,17 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,13 +3523,16 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
@@ -3421,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -3435,11 +3555,11 @@
       <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="L52" s="3">
+        <v>100</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3453,8 +3573,8 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="R52" s="3">
+        <v>0</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3468,14 +3588,17 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,56 +3665,59 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E54" s="3">
         <v>9500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>28200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,56 +3792,57 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1100</v>
       </c>
       <c r="K57" s="3">
         <v>1100</v>
       </c>
       <c r="L57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M57" s="3">
         <v>1600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>500</v>
       </c>
       <c r="N57" s="3">
         <v>500</v>
       </c>
       <c r="O57" s="3">
+        <v>500</v>
+      </c>
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3730,8 +3861,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3742,28 +3876,28 @@
         <v>200</v>
       </c>
       <c r="F58" s="3">
+        <v>200</v>
+      </c>
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>700</v>
-      </c>
-      <c r="H58" s="3">
-        <v>800</v>
       </c>
       <c r="I58" s="3">
         <v>800</v>
       </c>
       <c r="J58" s="3">
+        <v>800</v>
+      </c>
+      <c r="K58" s="3">
         <v>900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>600</v>
-      </c>
-      <c r="M58" s="3">
-        <v>500</v>
       </c>
       <c r="N58" s="3">
         <v>500</v>
@@ -3772,13 +3906,13 @@
         <v>500</v>
       </c>
       <c r="P58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q58" s="3">
         <v>400</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>400</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3798,56 +3932,59 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>700</v>
       </c>
       <c r="F59" s="3">
         <v>700</v>
       </c>
       <c r="G59" s="3">
+        <v>700</v>
+      </c>
+      <c r="H59" s="3">
         <v>1400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1500</v>
       </c>
       <c r="I59" s="3">
         <v>1500</v>
       </c>
       <c r="J59" s="3">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="K59" s="3">
         <v>700</v>
       </c>
       <c r="L59" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="M59" s="3">
         <v>1100</v>
       </c>
       <c r="N59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O59" s="3">
         <v>1500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,56 +4003,59 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2000</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,8 +4074,11 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3943,47 +4086,47 @@
         <v>300</v>
       </c>
       <c r="E61" s="3">
+        <v>300</v>
+      </c>
+      <c r="F61" s="3">
         <v>400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>800</v>
-      </c>
-      <c r="G61" s="3">
-        <v>1400</v>
       </c>
       <c r="H61" s="3">
         <v>1400</v>
       </c>
       <c r="I61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J61" s="3">
         <v>1500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1400</v>
-      </c>
-      <c r="L61" s="3">
-        <v>1500</v>
       </c>
       <c r="M61" s="3">
         <v>1500</v>
       </c>
       <c r="N61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O61" s="3">
         <v>1600</v>
-      </c>
-      <c r="O61" s="3">
-        <v>1700</v>
       </c>
       <c r="P61" s="3">
         <v>1700</v>
       </c>
       <c r="Q61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R61" s="3">
         <v>1800</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4002,37 +4145,40 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>1600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2800</v>
-      </c>
-      <c r="L62" s="3">
-        <v>100</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
@@ -4049,8 +4195,8 @@
       <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>100</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,46 +4429,49 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4200</v>
-      </c>
-      <c r="O66" s="3">
-        <v>3800</v>
       </c>
       <c r="P66" s="3">
         <v>3800</v>
@@ -4321,8 +4479,8 @@
       <c r="Q66" s="3">
         <v>3800</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
+      <c r="R66" s="3">
+        <v>3800</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,56 +4811,59 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-49100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-48000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-48600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-45400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-43400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-37200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-38100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-34800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-32500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-19600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-14700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-12000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-11000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,56 +5095,59 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E76" s="3">
         <v>6500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>24400</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45716</v>
+      </c>
+      <c r="E80" s="2">
         <v>45626</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45535</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45443</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45351</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45260</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45169</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45077</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44985</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44895</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44804</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44712</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44620</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44530</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44439</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44347</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44255</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44165</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43524</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43434</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>100</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5224,10 +5423,10 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -5236,10 +5435,10 @@
         <v>200</v>
       </c>
       <c r="I83" s="3">
+        <v>200</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -5260,7 +5459,7 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R83" s="3">
         <v>100</v>
@@ -5271,8 +5470,8 @@
       <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>100</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,65 +5837,68 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-3000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1500</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5691,8 +5908,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +5937,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5726,55 +5947,55 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-200</v>
       </c>
       <c r="G91" s="3">
         <v>-200</v>
       </c>
       <c r="H91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-200</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
       </c>
       <c r="L91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,64 +6148,67 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6044,8 +6278,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,65 +6530,68 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E100" s="3">
         <v>4700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>26600</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6355,8 +6601,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6384,8 +6633,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6423,65 +6672,68 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>25100</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6489,6 +6741,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>VMAR</t>
   </si>
@@ -656,167 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E7" s="2">
         <v>45716</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45626</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45535</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45443</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45351</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45260</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45169</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45077</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44985</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44895</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44804</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44712</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44620</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44530</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44439</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44347</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44255</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44165</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43524</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43434</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>200</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
       </c>
       <c r="F8" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3">
         <v>800</v>
       </c>
       <c r="H8" s="3">
+        <v>800</v>
+      </c>
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>600</v>
-      </c>
-      <c r="T8" s="3">
-        <v>200</v>
       </c>
       <c r="U8" s="3">
         <v>200</v>
@@ -825,30 +829,33 @@
         <v>200</v>
       </c>
       <c r="W8" s="3">
+        <v>200</v>
+      </c>
+      <c r="X8" s="3">
         <v>700</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E9" s="3">
         <v>100</v>
       </c>
       <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
         <v>500</v>
-      </c>
-      <c r="G9" s="3">
-        <v>400</v>
       </c>
       <c r="H9" s="3">
         <v>400</v>
@@ -857,55 +864,58 @@
         <v>400</v>
       </c>
       <c r="J9" s="3">
+        <v>400</v>
+      </c>
+      <c r="K9" s="3">
         <v>800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>400</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -916,67 +926,70 @@
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3">
         <v>300</v>
       </c>
       <c r="H10" s="3">
+        <v>300</v>
+      </c>
+      <c r="I10" s="3">
         <v>200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
       <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1000</v>
-      </c>
-      <c r="S10" s="3">
-        <v>100</v>
       </c>
       <c r="T10" s="3">
         <v>100</v>
       </c>
       <c r="U10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10" s="3">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
         <v>100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>300</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1011,58 +1025,58 @@
         <v>500</v>
       </c>
       <c r="E12" s="3">
+        <v>500</v>
+      </c>
+      <c r="F12" s="3">
         <v>200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1600</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
       <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>-100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3">
-        <v>0</v>
-      </c>
       <c r="U12" s="3">
         <v>0</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
+      <c r="V12" s="3">
+        <v>0</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1161,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1155,47 +1175,47 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>4600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>1900</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1215,8 +1235,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1230,22 +1253,22 @@
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
       </c>
       <c r="K15" s="3">
+        <v>100</v>
+      </c>
+      <c r="L15" s="3">
         <v>200</v>
-      </c>
-      <c r="L15" s="3">
-        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>100</v>
@@ -1254,7 +1277,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1263,11 +1286,11 @@
         <v>0</v>
       </c>
       <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
         <v>100</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
       <c r="T15" s="3">
         <v>0</v>
       </c>
@@ -1280,14 +1303,17 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2900</v>
-      </c>
-      <c r="P17" s="3">
-        <v>3300</v>
       </c>
       <c r="Q17" s="3">
         <v>3300</v>
       </c>
       <c r="R17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="S17" s="3">
         <v>4400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-3500</v>
       </c>
       <c r="K18" s="3">
         <v>-3500</v>
       </c>
       <c r="L18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="M18" s="3">
         <v>-2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>100</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,41 +1512,42 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1544,76 +1578,79 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-3100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-4800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1400</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
+      <c r="W21" s="3">
+        <v>0</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
@@ -1621,13 +1658,16 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1639,22 +1679,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
       <c r="J22" s="3">
         <v>0</v>
       </c>
       <c r="K22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>100</v>
       </c>
       <c r="M22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1692,79 +1732,85 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>100</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1778,44 +1824,44 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>-100</v>
       </c>
       <c r="L24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -1828,14 +1874,17 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
+      <c r="X24" s="3">
+        <v>0</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>100</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>100</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2150,11 +2211,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,41 +2398,44 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2396,85 +2466,91 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>100</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>100</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E38" s="2">
         <v>45716</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45626</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45535</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45443</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45351</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45260</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45169</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45077</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44985</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44895</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44804</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44712</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44620</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44530</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44439</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44347</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44255</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44165</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43524</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43434</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,59 +2831,60 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E41" s="3">
         <v>10600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>700</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13200</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,8 +2903,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2875,8 +2965,8 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
+      <c r="V42" s="3">
+        <v>0</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
@@ -2887,59 +2977,62 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
+        <v>200</v>
+      </c>
+      <c r="G43" s="3">
         <v>100</v>
-      </c>
-      <c r="G43" s="3">
-        <v>300</v>
       </c>
       <c r="H43" s="3">
         <v>300</v>
       </c>
       <c r="I43" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="J43" s="3">
         <v>500</v>
       </c>
       <c r="K43" s="3">
+        <v>500</v>
+      </c>
+      <c r="L43" s="3">
         <v>600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>300</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2958,59 +3051,62 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2000</v>
-      </c>
-      <c r="L44" s="3">
-        <v>1900</v>
       </c>
       <c r="M44" s="3">
         <v>1900</v>
       </c>
       <c r="N44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O44" s="3">
         <v>1500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1400</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3029,8 +3125,11 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3040,11 +3139,11 @@
       <c r="E45" s="3">
         <v>0</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
+      <c r="F45" s="3">
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
@@ -3062,26 +3161,26 @@
         <v>0</v>
       </c>
       <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3100,59 +3199,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E46" s="3">
         <v>17800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15500</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3171,8 +3273,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3203,26 +3308,26 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>2000</v>
-      </c>
-      <c r="N47" s="3">
-        <v>1900</v>
       </c>
       <c r="O47" s="3">
         <v>1900</v>
       </c>
       <c r="P47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q47" s="3">
         <v>1500</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>2100</v>
       </c>
       <c r="R47" s="3">
         <v>2100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>2100</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -3236,49 +3341,52 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>3300</v>
       </c>
       <c r="I48" s="3">
         <v>3300</v>
       </c>
       <c r="J48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K48" s="3">
         <v>3500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3500</v>
-      </c>
-      <c r="N48" s="3">
-        <v>3300</v>
       </c>
       <c r="O48" s="3">
         <v>3300</v>
@@ -3287,13 +3395,13 @@
         <v>3300</v>
       </c>
       <c r="Q48" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="R48" s="3">
         <v>3100</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+      <c r="S48" s="3">
+        <v>3100</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -3313,8 +3421,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3328,16 +3439,16 @@
         <v>600</v>
       </c>
       <c r="G49" s="3">
+        <v>600</v>
+      </c>
+      <c r="H49" s="3">
         <v>3900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7800</v>
-      </c>
-      <c r="J49" s="3">
-        <v>7900</v>
       </c>
       <c r="K49" s="3">
         <v>7900</v>
@@ -3349,22 +3460,22 @@
         <v>7900</v>
       </c>
       <c r="N49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="O49" s="3">
         <v>7600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7400</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>7500</v>
       </c>
       <c r="R49" s="3">
         <v>7500</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
+      <c r="S49" s="3">
+        <v>7500</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
@@ -3378,14 +3489,17 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,16 +3643,19 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -3544,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
@@ -3558,11 +3678,11 @@
       <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -3576,8 +3696,8 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
@@ -3591,14 +3711,17 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,59 +3791,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E54" s="3">
         <v>19600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>24400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>28200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,8 +3865,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,59 +3923,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1100</v>
       </c>
       <c r="L57" s="3">
         <v>1100</v>
       </c>
       <c r="M57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N57" s="3">
         <v>1600</v>
-      </c>
-      <c r="N57" s="3">
-        <v>500</v>
       </c>
       <c r="O57" s="3">
         <v>500</v>
       </c>
       <c r="P57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +3995,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3879,28 +4013,28 @@
         <v>200</v>
       </c>
       <c r="G58" s="3">
+        <v>200</v>
+      </c>
+      <c r="H58" s="3">
         <v>400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>700</v>
-      </c>
-      <c r="I58" s="3">
-        <v>800</v>
       </c>
       <c r="J58" s="3">
         <v>800</v>
       </c>
       <c r="K58" s="3">
+        <v>800</v>
+      </c>
+      <c r="L58" s="3">
         <v>900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>600</v>
-      </c>
-      <c r="N58" s="3">
-        <v>500</v>
       </c>
       <c r="O58" s="3">
         <v>500</v>
@@ -3909,13 +4043,13 @@
         <v>500</v>
       </c>
       <c r="Q58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R58" s="3">
         <v>400</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>400</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3935,59 +4069,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E59" s="3">
         <v>700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>700</v>
       </c>
       <c r="G59" s="3">
         <v>700</v>
       </c>
       <c r="H59" s="3">
+        <v>700</v>
+      </c>
+      <c r="I59" s="3">
         <v>1400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1500</v>
       </c>
       <c r="J59" s="3">
         <v>1500</v>
       </c>
       <c r="K59" s="3">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="L59" s="3">
         <v>700</v>
       </c>
       <c r="M59" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="N59" s="3">
         <v>1100</v>
       </c>
       <c r="O59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P59" s="3">
         <v>1500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>900</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4006,59 +4143,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4077,59 +4217,62 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E61" s="3">
         <v>300</v>
       </c>
       <c r="F61" s="3">
+        <v>300</v>
+      </c>
+      <c r="G61" s="3">
         <v>400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>800</v>
-      </c>
-      <c r="H61" s="3">
-        <v>1400</v>
       </c>
       <c r="I61" s="3">
         <v>1400</v>
       </c>
       <c r="J61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K61" s="3">
         <v>1500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1400</v>
-      </c>
-      <c r="M61" s="3">
-        <v>1500</v>
       </c>
       <c r="N61" s="3">
         <v>1500</v>
       </c>
       <c r="O61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P61" s="3">
         <v>1600</v>
-      </c>
-      <c r="P61" s="3">
-        <v>1700</v>
       </c>
       <c r="Q61" s="3">
         <v>1700</v>
       </c>
       <c r="R61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S61" s="3">
         <v>1800</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4148,40 +4291,43 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1200</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2800</v>
-      </c>
-      <c r="M62" s="3">
-        <v>100</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
@@ -4198,8 +4344,8 @@
       <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="S62" s="3">
+        <v>100</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,49 +4587,52 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E66" s="3">
         <v>3100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4200</v>
-      </c>
-      <c r="P66" s="3">
-        <v>3800</v>
       </c>
       <c r="Q66" s="3">
         <v>3800</v>
@@ -4482,8 +4640,8 @@
       <c r="R66" s="3">
         <v>3800</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
+      <c r="S66" s="3">
+        <v>3800</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
@@ -4503,8 +4661,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,59 +4985,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-56700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-49100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-48000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-48600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-45400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-43400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-37200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-38100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-34800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-32500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-19600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-14700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-12000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-8400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-7100</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4885,8 +5059,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,59 +5281,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E76" s="3">
         <v>16400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>24400</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5169,8 +5355,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E80" s="2">
         <v>45716</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45626</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45535</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45443</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45351</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45260</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45169</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45077</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44985</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44895</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44804</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44712</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44620</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44530</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44439</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44347</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44255</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44165</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43524</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43434</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>100</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5612,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5426,10 +5625,10 @@
         <v>200</v>
       </c>
       <c r="F83" s="3">
+        <v>200</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
@@ -5438,10 +5637,10 @@
         <v>200</v>
       </c>
       <c r="J83" s="3">
+        <v>200</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>200</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
@@ -5462,7 +5661,7 @@
         <v>200</v>
       </c>
       <c r="R83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S83" s="3">
         <v>100</v>
@@ -5473,8 +5672,8 @@
       <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>100</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,68 +6054,71 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1500</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5911,8 +6128,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,67 +6158,68 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,67 +6378,70 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6222,8 +6452,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6281,8 +6515,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,68 +6776,71 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>14000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>26600</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6604,8 +6850,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6636,8 +6885,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6675,68 +6924,71 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E102" s="3">
         <v>10000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>25100</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6744,6 +6996,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
   <si>
     <t>VMAR</t>
   </si>
@@ -656,340 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45900</v>
+      </c>
+      <c r="F7" s="2">
         <v>45808</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45716</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45626</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45535</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45443</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45351</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45260</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45169</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45077</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44985</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44895</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44804</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44712</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44620</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44530</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44439</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44347</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44255</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44165</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43524</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43434</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
+        <v>700</v>
+      </c>
+      <c r="J8" s="3">
         <v>800</v>
       </c>
-      <c r="H8" s="3">
-        <v>800</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1600</v>
-      </c>
-      <c r="L8" s="3">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="3">
-        <v>600</v>
       </c>
       <c r="N8" s="3">
         <v>1000</v>
       </c>
       <c r="O8" s="3">
+        <v>600</v>
+      </c>
+      <c r="P8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q8" s="3">
         <v>2500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>600</v>
-      </c>
-      <c r="U8" s="3">
-        <v>200</v>
-      </c>
-      <c r="V8" s="3">
-        <v>200</v>
       </c>
       <c r="W8" s="3">
         <v>200</v>
       </c>
       <c r="X8" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z8" s="3">
         <v>700</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>400</v>
       </c>
       <c r="J9" s="3">
         <v>400</v>
       </c>
       <c r="K9" s="3">
+        <v>400</v>
+      </c>
+      <c r="L9" s="3">
+        <v>400</v>
+      </c>
+      <c r="M9" s="3">
         <v>800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>400</v>
-      </c>
-      <c r="U9" s="3">
-        <v>100</v>
-      </c>
-      <c r="V9" s="3">
-        <v>200</v>
       </c>
       <c r="W9" s="3">
         <v>100</v>
       </c>
       <c r="X9" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z9" s="3">
         <v>400</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
       </c>
       <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
         <v>300</v>
-      </c>
-      <c r="H10" s="3">
-        <v>300</v>
-      </c>
-      <c r="I10" s="3">
-        <v>200</v>
       </c>
       <c r="J10" s="3">
         <v>300</v>
       </c>
       <c r="K10" s="3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="L10" s="3">
         <v>300</v>
       </c>
       <c r="M10" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="N10" s="3">
+        <v>300</v>
+      </c>
+      <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>100</v>
-      </c>
-      <c r="U10" s="3">
-        <v>100</v>
-      </c>
-      <c r="V10" s="3">
-        <v>0</v>
       </c>
       <c r="W10" s="3">
         <v>100</v>
       </c>
       <c r="X10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="3">
         <v>300</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,73 +1041,75 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
-      </c>
-      <c r="K12" s="3">
-        <v>500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>600</v>
       </c>
       <c r="M12" s="3">
         <v>500</v>
       </c>
       <c r="N12" s="3">
+        <v>600</v>
+      </c>
+      <c r="O12" s="3">
+        <v>500</v>
+      </c>
+      <c r="P12" s="3">
         <v>2700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1600</v>
       </c>
-      <c r="P12" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
         <v>100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>-100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3">
-        <v>0</v>
-      </c>
-      <c r="V12" s="3">
-        <v>0</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
+      <c r="W12" s="3">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
@@ -1090,8 +1117,14 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,64 +1197,70 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>15900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>4600</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>3100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>1900</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1238,16 +1277,22 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1256,47 +1301,47 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
+        <v>100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>100</v>
+      </c>
+      <c r="J15" s="3">
         <v>200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>100</v>
-      </c>
-      <c r="L15" s="3">
-        <v>200</v>
       </c>
       <c r="M15" s="3">
         <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="O15" s="3">
         <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
       <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
         <v>100</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
-      </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
       <c r="V15" s="3">
         <v>0</v>
       </c>
@@ -1306,14 +1351,20 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1388,170 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F17" s="3">
         <v>2900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K17" s="3">
         <v>2900</v>
       </c>
-      <c r="H17" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
+        <v>3900</v>
+      </c>
+      <c r="M17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N17" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>5300</v>
+      </c>
+      <c r="R17" s="3">
         <v>2900</v>
       </c>
-      <c r="J17" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K17" s="3">
-        <v>5100</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="S17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="U17" s="3">
         <v>4400</v>
       </c>
-      <c r="M17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="N17" s="3">
-        <v>6000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>5300</v>
-      </c>
-      <c r="P17" s="3">
-        <v>2900</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="R17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="S17" s="3">
-        <v>4400</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-3000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-2000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-5000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-2800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-2500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-2800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-3300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,47 +1578,49 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="F20" s="3">
         <v>2500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-4000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-3900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1581,100 +1648,112 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-5200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-2400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J21" s="3">
         <v>-2300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-4800</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-1200</v>
       </c>
       <c r="Q21" s="3">
         <v>-2600</v>
       </c>
       <c r="R21" s="3">
-        <v>-2300</v>
+        <v>-1200</v>
       </c>
       <c r="S21" s="3">
         <v>-2600</v>
       </c>
       <c r="T21" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="V21" s="3">
         <v>-3400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-3300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-1400</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
+      <c r="Y21" s="3">
+        <v>0</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>700</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
       <c r="G22" s="3">
         <v>0</v>
       </c>
@@ -1682,26 +1761,26 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1735,82 +1814,94 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-2500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="L23" s="3">
+        <v>700</v>
+      </c>
+      <c r="M23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="S23" s="3">
         <v>-2700</v>
       </c>
-      <c r="H23" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>700</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="T23" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="U23" s="3">
         <v>-2800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="V23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="W23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="X23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q23" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1827,47 +1918,47 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -1877,14 +1968,20 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2054,174 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-2500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-4900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-5000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-3500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-3400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-2500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-2700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-6200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-4900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-5000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-3500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-3400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2294,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2214,14 +2335,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2253,8 +2374,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2454,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,47 +2534,53 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>4000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>3900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2469,88 +2608,100 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-2500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-6200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-4900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-5000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-3500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-3400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2774,179 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-2500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-6200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-4900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-5000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-3500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-3400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45900</v>
+      </c>
+      <c r="F38" s="2">
         <v>45808</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45716</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45626</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45535</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45443</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45351</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45260</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45169</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45077</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44985</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44895</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44804</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44712</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44620</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44530</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44439</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44347</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44255</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44165</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43524</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43434</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2973,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,65 +3003,67 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F41" s="3">
         <v>7900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>700</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>3000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>5800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>7100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>10600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>13200</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2906,8 +3079,14 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2968,11 +3147,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
@@ -2980,65 +3159,71 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>600</v>
-      </c>
-      <c r="M43" s="3">
-        <v>800</v>
-      </c>
-      <c r="N43" s="3">
-        <v>700</v>
       </c>
       <c r="O43" s="3">
         <v>800</v>
       </c>
       <c r="P43" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="Q43" s="3">
         <v>800</v>
       </c>
       <c r="R43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S43" s="3">
+        <v>800</v>
+      </c>
+      <c r="T43" s="3">
         <v>700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>300</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,65 +3239,71 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>39600</v>
+      </c>
+      <c r="F44" s="3">
         <v>7000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>6700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>4500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>4000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>3500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>2200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>2000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>1400</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3128,28 +3319,34 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F45" s="3">
         <v>0</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
+      <c r="G45" s="3">
+        <v>0</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3">
         <v>0</v>
@@ -3164,29 +3361,29 @@
         <v>0</v>
       </c>
       <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>2500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>2100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3202,65 +3399,71 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>59000</v>
+      </c>
+      <c r="F46" s="3">
         <v>15800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>17800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>7500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>11800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>12200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>14100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>15500</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3276,8 +3479,14 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3311,30 +3520,30 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>2000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>2100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>2100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3344,71 +3553,77 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1300</v>
+        <v>13200</v>
       </c>
       <c r="E48" s="3">
-        <v>1200</v>
+        <v>10400</v>
       </c>
       <c r="F48" s="3">
         <v>1300</v>
       </c>
       <c r="G48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I48" s="3">
         <v>1400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3700</v>
-      </c>
-      <c r="M48" s="3">
-        <v>3300</v>
-      </c>
-      <c r="N48" s="3">
-        <v>3500</v>
       </c>
       <c r="O48" s="3">
         <v>3300</v>
       </c>
       <c r="P48" s="3">
-        <v>3300</v>
+        <v>3500</v>
       </c>
       <c r="Q48" s="3">
         <v>3300</v>
       </c>
       <c r="R48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="S48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T48" s="3">
         <v>3100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3100</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3424,16 +3639,22 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F49" s="3">
         <v>600</v>
@@ -3442,19 +3663,19 @@
         <v>600</v>
       </c>
       <c r="H49" s="3">
+        <v>600</v>
+      </c>
+      <c r="I49" s="3">
+        <v>600</v>
+      </c>
+      <c r="J49" s="3">
         <v>3900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>7800</v>
-      </c>
-      <c r="K49" s="3">
-        <v>7900</v>
-      </c>
-      <c r="L49" s="3">
-        <v>7900</v>
       </c>
       <c r="M49" s="3">
         <v>7900</v>
@@ -3463,25 +3684,25 @@
         <v>7900</v>
       </c>
       <c r="O49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="P49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="Q49" s="3">
         <v>7600</v>
-      </c>
-      <c r="P49" s="3">
-        <v>7500</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>7400</v>
       </c>
       <c r="R49" s="3">
         <v>7500</v>
       </c>
       <c r="S49" s="3">
+        <v>7400</v>
+      </c>
+      <c r="T49" s="3">
         <v>7500</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>7500</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -3492,14 +3713,20 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3799,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,31 +3879,37 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="D52" s="3">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>100</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -3681,14 +3920,14 @@
       <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>100</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -3699,11 +3938,11 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
@@ -3714,14 +3953,20 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,65 +4039,71 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>69900</v>
+      </c>
+      <c r="F54" s="3">
         <v>17800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>19600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>9500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>8500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>12600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>15700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>16900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>17800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>16100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>17400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>18200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>21200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>24500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>24400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>26900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>28200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3868,8 +4119,14 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4153,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,65 +4183,67 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>400</v>
       </c>
       <c r="R57" s="3">
         <v>500</v>
       </c>
       <c r="S57" s="3">
+        <v>400</v>
+      </c>
+      <c r="T57" s="3">
+        <v>500</v>
+      </c>
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,16 +4259,22 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>25600</v>
       </c>
       <c r="E58" s="3">
-        <v>200</v>
+        <v>2300</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
@@ -4016,47 +4283,47 @@
         <v>200</v>
       </c>
       <c r="H58" s="3">
+        <v>200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>200</v>
+      </c>
+      <c r="J58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>600</v>
-      </c>
-      <c r="O58" s="3">
-        <v>500</v>
-      </c>
-      <c r="P58" s="3">
-        <v>500</v>
       </c>
       <c r="Q58" s="3">
         <v>500</v>
       </c>
       <c r="R58" s="3">
+        <v>500</v>
+      </c>
+      <c r="S58" s="3">
+        <v>500</v>
+      </c>
+      <c r="T58" s="3">
         <v>400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>400</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4072,65 +4339,71 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>38800</v>
+      </c>
+      <c r="F59" s="3">
         <v>2900</v>
-      </c>
-      <c r="E59" s="3">
-        <v>700</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1000</v>
       </c>
       <c r="G59" s="3">
         <v>700</v>
       </c>
       <c r="H59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1100</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1500</v>
       </c>
       <c r="Q59" s="3">
         <v>1100</v>
       </c>
       <c r="R59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>900</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4146,64 +4419,70 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>49700</v>
+      </c>
+      <c r="F60" s="3">
         <v>4000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2600</v>
       </c>
-      <c r="G60" s="3">
-        <v>4200</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
+        <v>5900</v>
+      </c>
+      <c r="J60" s="3">
         <v>2900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>2000</v>
-      </c>
-      <c r="R60" s="3">
-        <v>1900</v>
       </c>
       <c r="S60" s="3">
         <v>2000</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
+      <c r="T60" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U60" s="3">
+        <v>2000</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
@@ -4220,65 +4499,71 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F61" s="3">
         <v>200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1800</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4294,46 +4579,52 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1200</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1600</v>
-      </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>6100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>5900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>4100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2800</v>
-      </c>
-      <c r="N62" s="3">
-        <v>100</v>
-      </c>
-      <c r="O62" s="3">
-        <v>100</v>
       </c>
       <c r="P62" s="3">
         <v>100</v>
@@ -4347,11 +4638,11 @@
       <c r="S62" s="3">
         <v>100</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+      <c r="T62" s="3">
+        <v>100</v>
+      </c>
+      <c r="U62" s="3">
+        <v>100</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
@@ -4368,8 +4659,14 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4739,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4819,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,64 +4899,70 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>61500</v>
+      </c>
+      <c r="F66" s="3">
         <v>5500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>9800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>9200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>7100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>7700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>4200</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>3800</v>
-      </c>
-      <c r="R66" s="3">
-        <v>3800</v>
       </c>
       <c r="S66" s="3">
         <v>3800</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
+      <c r="T66" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U66" s="3">
+        <v>3800</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
@@ -4664,8 +4979,14 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +5013,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +5089,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5169,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5249,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,65 +5329,71 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-75900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-71600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-56700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-49100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-48000</v>
       </c>
-      <c r="G72" s="3">
-        <v>-48600</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="J72" s="3">
         <v>-45400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-43400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-37200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-38100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-34800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-32500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-19600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-14700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-11000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-8400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-7100</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5062,8 +5409,14 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5489,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5569,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,65 +5649,71 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F76" s="3">
         <v>12300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>16400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>6500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>10400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>8500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>17500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>20300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>20600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>23100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>24400</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,8 +5729,14 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5809,179 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45900</v>
+      </c>
+      <c r="F80" s="2">
         <v>45808</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45716</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45626</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45535</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45443</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45351</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45260</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45169</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45077</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44985</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44895</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44804</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44712</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44620</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44530</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44439</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44347</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44255</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44165</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43524</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43434</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-2500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-6200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-4900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-5000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-3500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-3400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,40 +6008,42 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>200</v>
       </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
       </c>
       <c r="M83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3">
         <v>200</v>
@@ -5664,10 +6061,10 @@
         <v>200</v>
       </c>
       <c r="S83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="T83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
@@ -5675,11 +6072,11 @@
       <c r="V83" s="3">
         <v>100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="W83" s="3">
+        <v>100</v>
+      </c>
+      <c r="X83" s="3">
+        <v>100</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
@@ -5687,8 +6084,14 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +6164,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6244,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6324,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6404,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6484,94 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-4000</v>
       </c>
-      <c r="F89" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-400</v>
-      </c>
       <c r="H89" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-3200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-2400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-1900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1500</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,52 +6598,54 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-400</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
@@ -6216,16 +6657,16 @@
         <v>-100</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
@@ -6233,8 +6674,14 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6754,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,73 +6834,79 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J94" s="3">
         <v>600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-100</v>
-      </c>
       <c r="O94" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="P94" s="3">
         <v>-100</v>
       </c>
       <c r="Q94" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U94" s="3">
         <v>-3900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-2600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
@@ -6455,8 +6914,14 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6948,10 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6518,11 +6985,11 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6557,8 +7024,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +7104,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +7184,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,82 +7264,94 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>14000</v>
       </c>
-      <c r="F100" s="3">
-        <v>4700</v>
-      </c>
-      <c r="G100" s="3">
-        <v>200</v>
-      </c>
       <c r="H100" s="3">
+        <v>4800</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>4800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>3400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>4300</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-200</v>
       </c>
       <c r="P100" s="3">
         <v>-100</v>
       </c>
       <c r="Q100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>-500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>26600</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6888,11 +7385,11 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6927,78 +7424,90 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>10000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="K102" s="3">
-        <v>1300</v>
       </c>
       <c r="L102" s="3">
         <v>-1900</v>
       </c>
       <c r="M102" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N102" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="O102" s="3">
         <v>1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-3500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-4300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-5100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-2800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>25100</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VMAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>VMAR</t>
   </si>
@@ -656,187 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E7" s="2">
         <v>45991</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45900</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45808</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45716</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45626</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45535</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45443</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45351</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45260</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45169</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45077</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44985</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44895</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44804</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44712</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44620</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44530</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44439</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44347</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44255</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44165</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43524</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43434</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E8" s="3">
         <v>15700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>100</v>
       </c>
       <c r="H8" s="3">
         <v>100</v>
       </c>
       <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="3">
         <v>700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>600</v>
-      </c>
-      <c r="W8" s="3">
-        <v>200</v>
       </c>
       <c r="X8" s="3">
         <v>200</v>
@@ -845,39 +849,42 @@
         <v>200</v>
       </c>
       <c r="Z8" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA8" s="3">
         <v>700</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E9" s="3">
         <v>11500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>8700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>100</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
       </c>
       <c r="I9" s="3">
+        <v>100</v>
+      </c>
+      <c r="J9" s="3">
         <v>500</v>
-      </c>
-      <c r="J9" s="3">
-        <v>400</v>
       </c>
       <c r="K9" s="3">
         <v>400</v>
@@ -886,67 +893,70 @@
         <v>400</v>
       </c>
       <c r="M9" s="3">
+        <v>400</v>
+      </c>
+      <c r="N9" s="3">
         <v>800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>400</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E10" s="3">
         <v>4200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4800</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
       <c r="G10" s="3">
         <v>0</v>
       </c>
@@ -954,67 +964,70 @@
         <v>0</v>
       </c>
       <c r="I10" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
         <v>300</v>
       </c>
       <c r="K10" s="3">
+        <v>300</v>
+      </c>
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>300</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
       <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1000</v>
-      </c>
-      <c r="V10" s="3">
-        <v>100</v>
       </c>
       <c r="W10" s="3">
         <v>100</v>
       </c>
       <c r="X10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="3">
         <v>100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>300</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1052,67 +1066,67 @@
         <v>100</v>
       </c>
       <c r="E12" s="3">
+        <v>100</v>
+      </c>
+      <c r="F12" s="3">
         <v>-100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>500</v>
       </c>
       <c r="G12" s="3">
         <v>500</v>
       </c>
       <c r="H12" s="3">
+        <v>600</v>
+      </c>
+      <c r="I12" s="3">
         <v>200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>2700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1600</v>
       </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
       <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
         <v>100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>-100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>200</v>
       </c>
-      <c r="W12" s="3">
-        <v>0</v>
-      </c>
       <c r="X12" s="3">
         <v>0</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
+      <c r="Y12" s="3">
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,67 +1220,70 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>4500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>1900</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1283,19 +1303,22 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>900</v>
+      </c>
+      <c r="E15" s="3">
         <v>800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
@@ -1307,22 +1330,22 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M15" s="3">
         <v>100</v>
       </c>
       <c r="N15" s="3">
+        <v>100</v>
+      </c>
+      <c r="O15" s="3">
         <v>200</v>
-      </c>
-      <c r="O15" s="3">
-        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>100</v>
@@ -1331,7 +1354,7 @@
         <v>100</v>
       </c>
       <c r="R15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1340,11 +1363,11 @@
         <v>0</v>
       </c>
       <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
         <v>100</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
       <c r="W15" s="3">
         <v>0</v>
       </c>
@@ -1357,14 +1380,17 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>3</v>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E17" s="3">
         <v>18800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2900</v>
       </c>
-      <c r="G17" s="3">
-        <v>3000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I17" s="3">
         <v>2200</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2800</v>
       </c>
       <c r="J17" s="3">
         <v>2800</v>
       </c>
       <c r="K17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L17" s="3">
         <v>2900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2900</v>
-      </c>
-      <c r="S17" s="3">
-        <v>3300</v>
       </c>
       <c r="T17" s="3">
         <v>3300</v>
       </c>
       <c r="U17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="V17" s="3">
         <v>4400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>600</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2700</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3000</v>
-      </c>
       <c r="H18" s="3">
-        <v>-2100</v>
+        <v>-3100</v>
       </c>
       <c r="I18" s="3">
         <v>-2100</v>
       </c>
       <c r="J18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-3500</v>
       </c>
       <c r="N18" s="3">
         <v>-3500</v>
       </c>
       <c r="O18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="P18" s="3">
         <v>-2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>100</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,50 +1613,51 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1654,85 +1688,88 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
+      <c r="AA20" s="3">
+        <v>0</v>
       </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-2400</v>
-      </c>
       <c r="H21" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
+      <c r="Z21" s="3">
+        <v>0</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
@@ -1740,23 +1777,26 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
@@ -1767,22 +1807,22 @@
         <v>0</v>
       </c>
       <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1820,88 +1860,94 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="M23" s="3">
+        <v>700</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="R23" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="S23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="T23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="U23" s="3">
         <v>-2500</v>
       </c>
-      <c r="H23" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="L23" s="3">
-        <v>700</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="V23" s="3">
         <v>-2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="W23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="X23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-1400</v>
       </c>
-      <c r="S23" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="U23" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>100</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1924,44 +1970,44 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
         <v>-100</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
       <c r="Q24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>100</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -1974,14 +2020,17 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
+      <c r="AA24" s="3">
+        <v>0</v>
       </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="M26" s="3">
+        <v>800</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="R26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="T26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="H26" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="L26" s="3">
-        <v>800</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="V26" s="3">
         <v>-2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="W26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="X26" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-1400</v>
       </c>
-      <c r="S26" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="U26" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>100</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="M27" s="3">
+        <v>800</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="R27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="S27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="T27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="U27" s="3">
         <v>-2500</v>
       </c>
-      <c r="H27" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="L27" s="3">
-        <v>800</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="V27" s="3">
         <v>-2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="W27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="X27" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-1400</v>
       </c>
-      <c r="S27" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="U27" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>100</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2341,11 +2402,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,50 +2607,53 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2614,94 +2684,100 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
+      <c r="AA32" s="3">
+        <v>0</v>
       </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="M33" s="3">
+        <v>800</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="R33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="S33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="T33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="U33" s="3">
         <v>-2500</v>
       </c>
-      <c r="H33" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="L33" s="3">
-        <v>800</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="V33" s="3">
         <v>-2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="W33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="X33" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="U33" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>100</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="M35" s="3">
+        <v>800</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="R35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="S35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="T35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="U35" s="3">
         <v>-2500</v>
       </c>
-      <c r="H35" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="L35" s="3">
-        <v>800</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="V35" s="3">
         <v>-2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="W35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="X35" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="U35" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>100</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E38" s="2">
         <v>45991</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45900</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45808</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45716</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45626</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45535</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45443</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45351</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45260</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45169</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45077</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44985</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44895</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44804</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44712</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44620</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44530</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44439</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44347</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44255</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44165</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43524</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43434</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,68 +3091,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>700</v>
       </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
       <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13200</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3085,8 +3172,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3153,8 +3243,8 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
+      <c r="Y42" s="3">
+        <v>0</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
@@ -3165,68 +3255,71 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E43" s="3">
         <v>7100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>200</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
       </c>
       <c r="I43" s="3">
+        <v>200</v>
+      </c>
+      <c r="J43" s="3">
         <v>100</v>
-      </c>
-      <c r="J43" s="3">
-        <v>300</v>
       </c>
       <c r="K43" s="3">
         <v>300</v>
       </c>
       <c r="L43" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="M43" s="3">
         <v>500</v>
       </c>
       <c r="N43" s="3">
+        <v>500</v>
+      </c>
+      <c r="O43" s="3">
         <v>600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>300</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3245,68 +3338,71 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>32900</v>
+      </c>
+      <c r="E44" s="3">
         <v>35800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>39600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2000</v>
-      </c>
-      <c r="O44" s="3">
-        <v>1900</v>
       </c>
       <c r="P44" s="3">
         <v>1900</v>
       </c>
       <c r="Q44" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R44" s="3">
         <v>1500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1400</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,8 +3421,11 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3336,8 +3435,8 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
@@ -3345,11 +3444,11 @@
       <c r="H45" s="3">
         <v>0</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3367,26 +3466,26 @@
         <v>0</v>
       </c>
       <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>600</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3405,68 +3504,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E46" s="3">
         <v>45900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>59000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15500</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3485,8 +3587,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3526,26 +3631,26 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>2000</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>1900</v>
       </c>
       <c r="R47" s="3">
         <v>1900</v>
       </c>
       <c r="S47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T47" s="3">
         <v>1500</v>
-      </c>
-      <c r="T47" s="3">
-        <v>2100</v>
       </c>
       <c r="U47" s="3">
         <v>2100</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
+      <c r="V47" s="3">
+        <v>2100</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
@@ -3559,58 +3664,61 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E48" s="3">
         <v>13200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>3300</v>
       </c>
       <c r="L48" s="3">
         <v>3300</v>
       </c>
       <c r="M48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N48" s="3">
         <v>3500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3500</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>3300</v>
       </c>
       <c r="R48" s="3">
         <v>3300</v>
@@ -3619,13 +3727,13 @@
         <v>3300</v>
       </c>
       <c r="T48" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="U48" s="3">
         <v>3100</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
+      <c r="V48" s="3">
+        <v>3100</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
@@ -3645,19 +3753,22 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E49" s="3">
         <v>500</v>
       </c>
       <c r="F49" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G49" s="3">
         <v>600</v>
@@ -3669,16 +3780,16 @@
         <v>600</v>
       </c>
       <c r="J49" s="3">
+        <v>600</v>
+      </c>
+      <c r="K49" s="3">
         <v>3900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7800</v>
-      </c>
-      <c r="M49" s="3">
-        <v>7900</v>
       </c>
       <c r="N49" s="3">
         <v>7900</v>
@@ -3690,22 +3801,22 @@
         <v>7900</v>
       </c>
       <c r="Q49" s="3">
+        <v>7900</v>
+      </c>
+      <c r="R49" s="3">
         <v>7600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7400</v>
-      </c>
-      <c r="T49" s="3">
-        <v>7500</v>
       </c>
       <c r="U49" s="3">
         <v>7500</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="V49" s="3">
+        <v>7500</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
@@ -3719,14 +3830,17 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,8 +4002,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3896,14 +4016,14 @@
       <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="F52" s="3">
+        <v>100</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -3912,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
@@ -3926,11 +4046,11 @@
       <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -3944,8 +4064,8 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
+      <c r="V52" s="3">
+        <v>0</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
@@ -3959,14 +4079,17 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,68 +4168,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E54" s="3">
         <v>59700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>69900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>24500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>24400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>28200</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,68 +4315,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E57" s="3">
         <v>8900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
-      </c>
-      <c r="N57" s="3">
-        <v>1100</v>
       </c>
       <c r="O57" s="3">
         <v>1100</v>
       </c>
       <c r="P57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>500</v>
       </c>
       <c r="R57" s="3">
         <v>500</v>
       </c>
       <c r="S57" s="3">
+        <v>500</v>
+      </c>
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4265,19 +4396,22 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E58" s="3">
         <v>25600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2300</v>
-      </c>
-      <c r="F58" s="3">
-        <v>200</v>
       </c>
       <c r="G58" s="3">
         <v>200</v>
@@ -4289,28 +4423,28 @@
         <v>200</v>
       </c>
       <c r="J58" s="3">
+        <v>200</v>
+      </c>
+      <c r="K58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>700</v>
-      </c>
-      <c r="L58" s="3">
-        <v>800</v>
       </c>
       <c r="M58" s="3">
         <v>800</v>
       </c>
       <c r="N58" s="3">
+        <v>800</v>
+      </c>
+      <c r="O58" s="3">
         <v>900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>600</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>500</v>
       </c>
       <c r="R58" s="3">
         <v>500</v>
@@ -4319,13 +4453,13 @@
         <v>500</v>
       </c>
       <c r="T58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="U58" s="3">
         <v>400</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3">
+        <v>400</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -4345,68 +4479,71 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E59" s="3">
         <v>6400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>38800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1500</v>
       </c>
       <c r="M59" s="3">
         <v>1500</v>
       </c>
       <c r="N59" s="3">
-        <v>700</v>
+        <v>1500</v>
       </c>
       <c r="O59" s="3">
         <v>700</v>
       </c>
       <c r="P59" s="3">
-        <v>1100</v>
+        <v>700</v>
       </c>
       <c r="Q59" s="3">
         <v>1100</v>
       </c>
       <c r="R59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S59" s="3">
         <v>1500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4425,68 +4562,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E60" s="3">
         <v>41200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>49700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2000</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4505,68 +4645,71 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E61" s="3">
         <v>8900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>200</v>
-      </c>
-      <c r="G61" s="3">
-        <v>300</v>
       </c>
       <c r="H61" s="3">
         <v>300</v>
       </c>
       <c r="I61" s="3">
+        <v>300</v>
+      </c>
+      <c r="J61" s="3">
         <v>400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>800</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1400</v>
       </c>
       <c r="L61" s="3">
         <v>1400</v>
       </c>
       <c r="M61" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N61" s="3">
         <v>1500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1400</v>
-      </c>
-      <c r="P61" s="3">
-        <v>1500</v>
       </c>
       <c r="Q61" s="3">
         <v>1500</v>
       </c>
       <c r="R61" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S61" s="3">
         <v>1600</v>
-      </c>
-      <c r="S61" s="3">
-        <v>1700</v>
       </c>
       <c r="T61" s="3">
         <v>1700</v>
       </c>
       <c r="U61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V61" s="3">
         <v>1800</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4585,49 +4728,52 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E62" s="3">
         <v>5200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1200</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>6100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2800</v>
-      </c>
-      <c r="P62" s="3">
-        <v>100</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
@@ -4644,8 +4790,8 @@
       <c r="U62" s="3">
         <v>100</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
+      <c r="V62" s="3">
+        <v>100</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,58 +5060,61 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>49100</v>
+      </c>
+      <c r="E66" s="3">
         <v>55400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>61500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4200</v>
-      </c>
-      <c r="S66" s="3">
-        <v>3800</v>
       </c>
       <c r="T66" s="3">
         <v>3800</v>
@@ -4964,8 +5122,8 @@
       <c r="U66" s="3">
         <v>3800</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
+      <c r="V66" s="3">
+        <v>3800</v>
       </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,68 +5506,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-77800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-75900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-71600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-56700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-49100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-48000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-49900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-45400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-43400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-37200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-38100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-34800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-32500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-14700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-12000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-11000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-8400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,68 +5838,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E76" s="3">
         <v>4300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>23100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>24400</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E80" s="2">
         <v>45991</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45900</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45808</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45716</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45626</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45535</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45443</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45351</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45260</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45169</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45077</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44985</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44895</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44804</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44712</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44620</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44530</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44439</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44347</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44255</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44165</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43524</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43434</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="M81" s="3">
+        <v>800</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="O81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="R81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="S81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="T81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="U81" s="3">
         <v>-2500</v>
       </c>
-      <c r="H81" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="L81" s="3">
-        <v>800</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="V81" s="3">
         <v>-2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="W81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="X81" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="U81" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>100</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6208,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6019,10 +6218,10 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
         <v>200</v>
@@ -6031,10 +6230,10 @@
         <v>200</v>
       </c>
       <c r="I83" s="3">
+        <v>200</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>200</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -6043,10 +6242,10 @@
         <v>200</v>
       </c>
       <c r="M83" s="3">
+        <v>200</v>
+      </c>
+      <c r="N83" s="3">
         <v>100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>200</v>
       </c>
       <c r="O83" s="3">
         <v>200</v>
@@ -6067,7 +6266,7 @@
         <v>200</v>
       </c>
       <c r="U83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V83" s="3">
         <v>100</v>
@@ -6078,8 +6277,8 @@
       <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>100</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,77 +6704,80 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2800</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-4000</v>
       </c>
       <c r="H89" s="3">
         <v>-4200</v>
       </c>
       <c r="I89" s="3">
-        <v>0</v>
+        <v>-4200</v>
       </c>
       <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6570,8 +6787,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,76 +6820,77 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-200</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-200</v>
       </c>
       <c r="O91" s="3">
         <v>-200</v>
       </c>
       <c r="P91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,76 +7067,79 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>3800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6991,8 +7225,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,77 +7513,80 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
-        <v>14000</v>
-      </c>
       <c r="H100" s="3">
+        <v>14100</v>
+      </c>
+      <c r="I100" s="3">
         <v>4800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>-500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>26600</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7350,8 +7596,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7391,8 +7640,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7430,77 +7679,80 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3200</v>
       </c>
-      <c r="G102" s="3">
-        <v>10000</v>
-      </c>
       <c r="H102" s="3">
+        <v>9900</v>
+      </c>
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>25100</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7508,6 +7760,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
